--- a/files/九龙-红磡-映汇.xlsx
+++ b/files/九龙-红磡-映汇.xlsx
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1660,34 +1660,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H16" s="5" t="n">
+        <v>6858000</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>24669</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>6172200</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>22202</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2476,7 +2468,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -2484,34 +2476,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H28" s="5" t="n">
+        <v>6780000</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>24388</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>6102000</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>21950</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -3300,7 +3284,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -3308,34 +3292,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H40" s="5" t="n">
+        <v>6740000</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>24245</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>6066000</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>21820</v>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -3992,7 +3968,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -4000,34 +3976,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H50" s="5" t="n">
+        <v>9619000</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>24920</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K50" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L50" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>8657100</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>22428</v>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
@@ -4124,7 +4092,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -4132,34 +4100,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H52" s="5" t="n">
+        <v>6701000</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>24104</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K52" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L52" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>6030900</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>21694</v>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -4746,7 +4706,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -4754,34 +4714,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H61" s="5" t="n">
+        <v>11530000</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>27584</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K61" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L61" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>10377000</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>24825</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -4816,7 +4768,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -4824,34 +4776,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I62" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H62" s="5" t="n">
+        <v>9425000</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>24417</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K62" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L62" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>8482500</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>21975</v>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -4948,7 +4892,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -4956,34 +4900,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H64" s="5" t="n">
+        <v>6662000</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>23964</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K64" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L64" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>5995800</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>21568</v>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
@@ -5158,7 +5094,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -5166,34 +5102,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H67" s="5" t="n">
+        <v>7887000</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>24880</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L67" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>7098300</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>22392</v>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
@@ -5228,7 +5156,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -5236,34 +5164,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H68" s="5" t="n">
+        <v>10384000</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>26832</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K68" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L68" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>9345600</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>24149</v>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
@@ -5298,7 +5218,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -5306,34 +5226,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H69" s="5" t="n">
+        <v>9348000</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>25823</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L69" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>8413200</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>23241</v>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
@@ -5570,7 +5482,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -5578,34 +5490,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H73" s="5" t="n">
+        <v>11268000</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>26957</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>10141200</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>24261</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
@@ -5640,7 +5544,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -5648,34 +5552,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H74" s="5" t="n">
+        <v>9371000</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>24277</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>8433900</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>21849</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
@@ -5772,7 +5668,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -5780,34 +5676,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I76" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H76" s="5" t="n">
+        <v>6622000</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>23820</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K76" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L76" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>5959800</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>21438</v>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
@@ -5982,7 +5870,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -5990,34 +5878,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I79" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H79" s="5" t="n">
+        <v>7841000</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>24735</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K79" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L79" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>7056900</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>22262</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
@@ -6052,7 +5932,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -6060,34 +5940,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I80" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H80" s="5" t="n">
+        <v>10264000</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>26522</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K80" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L80" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>9237600</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>23870</v>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
@@ -6122,7 +5994,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -6130,34 +6002,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I81" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H81" s="5" t="n">
+        <v>9239000</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>25522</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K81" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L81" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>8315100</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>22970</v>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr">
@@ -6394,7 +6258,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -6402,34 +6266,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I85" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H85" s="5" t="n">
+        <v>11141000</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>26653</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L85" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>10026900</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>23988</v>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr">
@@ -6588,7 +6444,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -6596,34 +6452,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I88" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H88" s="5" t="n">
+        <v>6583000</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>23680</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K88" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L88" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>5924700</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>21312</v>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
@@ -6798,7 +6646,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -6806,34 +6654,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I91" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H91" s="5" t="n">
+        <v>7796000</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>24593</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K91" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L91" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>7016400</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>22134</v>
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N91" s="3" t="inlineStr">
@@ -6868,7 +6708,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
@@ -6876,34 +6716,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I92" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H92" s="5" t="n">
+        <v>10174000</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>26289</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K92" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L92" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>9156600</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>23660</v>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">
@@ -6938,7 +6770,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -6946,34 +6778,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I93" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H93" s="5" t="n">
+        <v>9157000</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>25296</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K93" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L93" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>8241300</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>22766</v>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N93" s="3" t="inlineStr">
@@ -7396,7 +7220,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
@@ -7404,34 +7228,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I100" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H100" s="5" t="n">
+        <v>6544000</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>23540</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K100" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L100" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>5889600</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>21186</v>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N100" s="3" t="inlineStr">
@@ -7606,7 +7422,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
@@ -7614,34 +7430,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I103" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H103" s="5" t="n">
+        <v>7750000</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>24448</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L103" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>6975000</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>22003</v>
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N103" s="3" t="inlineStr">
@@ -7676,7 +7484,7 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
@@ -7684,34 +7492,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I104" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H104" s="5" t="n">
+        <v>10113000</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>26132</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K104" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L104" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>9101700</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>23519</v>
       </c>
       <c r="M104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N104" s="3" t="inlineStr">
@@ -7746,7 +7546,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -7754,34 +7554,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H105" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I105" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H105" s="5" t="n">
+        <v>9102000</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>25144</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K105" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L105" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>8191800</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>22629</v>
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N105" s="3" t="inlineStr">
@@ -9728,7 +9520,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
@@ -9736,34 +9528,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H134" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I134" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H134" s="5" t="n">
+        <v>9231000</v>
+      </c>
+      <c r="I134" s="5" t="n">
+        <v>23915</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K134" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L134" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>8307900</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>21523</v>
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N134" s="3" t="inlineStr">
@@ -9860,7 +9644,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -9868,34 +9652,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H136" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I136" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H136" s="5" t="n">
+        <v>6422000</v>
+      </c>
+      <c r="I136" s="5" t="n">
+        <v>23101</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K136" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L136" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>5779800</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>20791</v>
       </c>
       <c r="M136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N136" s="3" t="inlineStr">
@@ -10140,7 +9916,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -10148,34 +9924,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H140" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I140" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H140" s="5" t="n">
+        <v>9933000</v>
+      </c>
+      <c r="I140" s="5" t="n">
+        <v>25667</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K140" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L140" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>8939700</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>23100</v>
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N140" s="3" t="inlineStr">
@@ -10210,7 +9978,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -10218,34 +9986,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H141" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I141" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H141" s="5" t="n">
+        <v>8938000</v>
+      </c>
+      <c r="I141" s="5" t="n">
+        <v>24691</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K141" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L141" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>8044200</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>22222</v>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N141" s="3" t="inlineStr">
@@ -10482,7 +10242,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
@@ -10490,34 +10250,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H145" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I145" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H145" s="5" t="n">
+        <v>10948000</v>
+      </c>
+      <c r="I145" s="5" t="n">
+        <v>26191</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K145" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L145" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>9853200</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>23572</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N145" s="3" t="inlineStr">
@@ -10552,7 +10304,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
@@ -10560,34 +10312,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H146" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I146" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H146" s="5" t="n">
+        <v>9070000</v>
+      </c>
+      <c r="I146" s="5" t="n">
+        <v>23497</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K146" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L146" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>8163000</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>21148</v>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N146" s="3" t="inlineStr">
@@ -10684,7 +10428,7 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
@@ -10692,34 +10436,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H148" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I148" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H148" s="5" t="n">
+        <v>6398000</v>
+      </c>
+      <c r="I148" s="5" t="n">
+        <v>23014</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K148" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L148" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>5758200</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <v>20713</v>
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N148" s="3" t="inlineStr">
@@ -10894,7 +10630,7 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
@@ -10902,34 +10638,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H151" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I151" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H151" s="5" t="n">
+        <v>7591000</v>
+      </c>
+      <c r="I151" s="5" t="n">
+        <v>23946</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K151" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L151" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>6831900</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>21552</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N151" s="3" t="inlineStr">
@@ -10964,7 +10692,7 @@
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
@@ -10972,34 +10700,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H152" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I152" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H152" s="5" t="n">
+        <v>9873000</v>
+      </c>
+      <c r="I152" s="5" t="n">
+        <v>25512</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K152" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L152" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="n">
+        <v>8885700</v>
+      </c>
+      <c r="L152" s="5" t="n">
+        <v>22960</v>
       </c>
       <c r="M152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N152" s="3" t="inlineStr">
@@ -11034,7 +10754,7 @@
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
@@ -11042,34 +10762,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H153" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I153" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H153" s="5" t="n">
+        <v>8883000</v>
+      </c>
+      <c r="I153" s="5" t="n">
+        <v>24539</v>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K153" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L153" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="n">
+        <v>7994700</v>
+      </c>
+      <c r="L153" s="5" t="n">
+        <v>22085</v>
       </c>
       <c r="M153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N153" s="3" t="inlineStr">
@@ -11306,7 +11018,7 @@
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
@@ -11314,34 +11026,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H157" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I157" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H157" s="5" t="n">
+        <v>10726000</v>
+      </c>
+      <c r="I157" s="5" t="n">
+        <v>25660</v>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K157" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L157" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>9653400</v>
+      </c>
+      <c r="L157" s="5" t="n">
+        <v>23094</v>
       </c>
       <c r="M157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N157" s="3" t="inlineStr">
@@ -11710,7 +11414,7 @@
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
@@ -11718,34 +11422,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H163" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I163" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H163" s="5" t="n">
+        <v>7568000</v>
+      </c>
+      <c r="I163" s="5" t="n">
+        <v>23874</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K163" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L163" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>6811200</v>
+      </c>
+      <c r="L163" s="5" t="n">
+        <v>21486</v>
       </c>
       <c r="M163" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N163" s="3" t="inlineStr">
@@ -11780,7 +11476,7 @@
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
@@ -11788,34 +11484,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I164" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H164" s="5" t="n">
+        <v>9693000</v>
+      </c>
+      <c r="I164" s="5" t="n">
+        <v>25047</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K164" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L164" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="n">
+        <v>8723700</v>
+      </c>
+      <c r="L164" s="5" t="n">
+        <v>22542</v>
       </c>
       <c r="M164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N164" s="3" t="inlineStr">
@@ -11850,7 +11538,7 @@
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
@@ -11858,34 +11546,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H165" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I165" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H165" s="5" t="n">
+        <v>8719000</v>
+      </c>
+      <c r="I165" s="5" t="n">
+        <v>24086</v>
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K165" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L165" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>7847100</v>
+      </c>
+      <c r="L165" s="5" t="n">
+        <v>21677</v>
       </c>
       <c r="M165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N165" s="3" t="inlineStr">
@@ -12518,7 +12198,7 @@
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
@@ -12526,34 +12206,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H175" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I175" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H175" s="5" t="n">
+        <v>7545000</v>
+      </c>
+      <c r="I175" s="5" t="n">
+        <v>23801</v>
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L175" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K175" s="5" t="n">
+        <v>6790500</v>
+      </c>
+      <c r="L175" s="5" t="n">
+        <v>21421</v>
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N175" s="3" t="inlineStr">
@@ -12588,7 +12260,7 @@
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
@@ -12596,34 +12268,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H176" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I176" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H176" s="5" t="n">
+        <v>9422000</v>
+      </c>
+      <c r="I176" s="5" t="n">
+        <v>24346</v>
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K176" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L176" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K176" s="5" t="n">
+        <v>8479800</v>
+      </c>
+      <c r="L176" s="5" t="n">
+        <v>21912</v>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N176" s="3" t="inlineStr">
@@ -12658,7 +12322,7 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
@@ -12666,34 +12330,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H177" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I177" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H177" s="5" t="n">
+        <v>8473000</v>
+      </c>
+      <c r="I177" s="5" t="n">
+        <v>23406</v>
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K177" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L177" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K177" s="5" t="n">
+        <v>7625700</v>
+      </c>
+      <c r="L177" s="5" t="n">
+        <v>21065</v>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N177" s="3" t="inlineStr">
@@ -13334,7 +12990,7 @@
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
@@ -13342,34 +12998,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H187" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I187" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H187" s="5" t="n">
+        <v>7522000</v>
+      </c>
+      <c r="I187" s="5" t="n">
+        <v>23729</v>
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K187" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L187" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K187" s="5" t="n">
+        <v>6769800</v>
+      </c>
+      <c r="L187" s="5" t="n">
+        <v>21356</v>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N187" s="3" t="inlineStr">
@@ -13474,7 +13122,7 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
@@ -13482,34 +13130,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H189" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I189" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H189" s="5" t="n">
+        <v>8514000</v>
+      </c>
+      <c r="I189" s="5" t="n">
+        <v>23519</v>
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K189" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L189" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K189" s="5" t="n">
+        <v>7662600</v>
+      </c>
+      <c r="L189" s="5" t="n">
+        <v>21167</v>
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N189" s="3" t="inlineStr">
@@ -14298,7 +13938,7 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -14306,34 +13946,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H201" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I201" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H201" s="5" t="n">
+        <v>8459000</v>
+      </c>
+      <c r="I201" s="5" t="n">
+        <v>23367</v>
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K201" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L201" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K201" s="5" t="n">
+        <v>7613100</v>
+      </c>
+      <c r="L201" s="5" t="n">
+        <v>21031</v>
       </c>
       <c r="M201" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N201" s="3" t="inlineStr">
@@ -14982,7 +14614,7 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -14990,34 +14622,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H211" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I211" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H211" s="5" t="n">
+        <v>7477000</v>
+      </c>
+      <c r="I211" s="5" t="n">
+        <v>23587</v>
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K211" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L211" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K211" s="5" t="n">
+        <v>6729300</v>
+      </c>
+      <c r="L211" s="5" t="n">
+        <v>21228</v>
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N211" s="3" t="inlineStr">
@@ -15052,7 +14676,7 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -15060,34 +14684,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H212" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I212" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H212" s="5" t="n">
+        <v>9212000</v>
+      </c>
+      <c r="I212" s="5" t="n">
+        <v>23804</v>
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K212" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L212" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K212" s="5" t="n">
+        <v>8290800</v>
+      </c>
+      <c r="L212" s="5" t="n">
+        <v>21423</v>
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N212" s="3" t="inlineStr">
@@ -15122,7 +14738,7 @@
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -15130,34 +14746,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H213" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I213" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H213" s="5" t="n">
+        <v>8282000</v>
+      </c>
+      <c r="I213" s="5" t="n">
+        <v>22878</v>
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K213" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L213" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K213" s="5" t="n">
+        <v>7453800</v>
+      </c>
+      <c r="L213" s="5" t="n">
+        <v>20591</v>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N213" s="3" t="inlineStr">
@@ -15806,7 +15414,7 @@
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
@@ -15814,34 +15422,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H223" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I223" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H223" s="5" t="n">
+        <v>7454000</v>
+      </c>
+      <c r="I223" s="5" t="n">
+        <v>23514</v>
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K223" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L223" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K223" s="5" t="n">
+        <v>6708600</v>
+      </c>
+      <c r="L223" s="5" t="n">
+        <v>21163</v>
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N223" s="3" t="inlineStr">
@@ -15876,7 +15476,7 @@
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -15884,34 +15484,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H224" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I224" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H224" s="5" t="n">
+        <v>9212000</v>
+      </c>
+      <c r="I224" s="5" t="n">
+        <v>23804</v>
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K224" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L224" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K224" s="5" t="n">
+        <v>8290800</v>
+      </c>
+      <c r="L224" s="5" t="n">
+        <v>21423</v>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N224" s="3" t="inlineStr">
@@ -15946,7 +15538,7 @@
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
@@ -15954,34 +15546,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H225" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I225" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H225" s="5" t="n">
+        <v>8282000</v>
+      </c>
+      <c r="I225" s="5" t="n">
+        <v>22878</v>
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K225" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L225" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K225" s="5" t="n">
+        <v>7453800</v>
+      </c>
+      <c r="L225" s="5" t="n">
+        <v>20591</v>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N225" s="3" t="inlineStr">
@@ -16622,7 +16206,7 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
@@ -16630,34 +16214,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H235" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I235" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H235" s="5" t="n">
+        <v>7454000</v>
+      </c>
+      <c r="I235" s="5" t="n">
+        <v>23514</v>
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K235" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L235" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K235" s="5" t="n">
+        <v>6708600</v>
+      </c>
+      <c r="L235" s="5" t="n">
+        <v>21163</v>
       </c>
       <c r="M235" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N235" s="3" t="inlineStr">
@@ -16692,7 +16268,7 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
@@ -16700,34 +16276,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H236" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I236" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H236" s="5" t="n">
+        <v>9092000</v>
+      </c>
+      <c r="I236" s="5" t="n">
+        <v>23494</v>
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K236" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L236" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K236" s="5" t="n">
+        <v>8182800</v>
+      </c>
+      <c r="L236" s="5" t="n">
+        <v>21144</v>
       </c>
       <c r="M236" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N236" s="3" t="inlineStr">
@@ -16762,7 +16330,7 @@
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
@@ -16770,34 +16338,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H237" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I237" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H237" s="5" t="n">
+        <v>8173000</v>
+      </c>
+      <c r="I237" s="5" t="n">
+        <v>22577</v>
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K237" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L237" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K237" s="5" t="n">
+        <v>7355700</v>
+      </c>
+      <c r="L237" s="5" t="n">
+        <v>20320</v>
       </c>
       <c r="M237" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N237" s="3" t="inlineStr">
@@ -17430,7 +16990,7 @@
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
@@ -17438,34 +16998,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H247" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I247" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H247" s="5" t="n">
+        <v>7420000</v>
+      </c>
+      <c r="I247" s="5" t="n">
+        <v>23407</v>
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K247" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L247" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K247" s="5" t="n">
+        <v>6678000</v>
+      </c>
+      <c r="L247" s="5" t="n">
+        <v>21066</v>
       </c>
       <c r="M247" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N247" s="3" t="inlineStr">
@@ -17500,7 +17052,7 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -17508,34 +17060,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H248" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I248" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H248" s="5" t="n">
+        <v>8972000</v>
+      </c>
+      <c r="I248" s="5" t="n">
+        <v>23183</v>
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K248" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L248" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K248" s="5" t="n">
+        <v>8074800</v>
+      </c>
+      <c r="L248" s="5" t="n">
+        <v>20865</v>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N248" s="3" t="inlineStr">
@@ -17570,7 +17114,7 @@
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
@@ -17578,34 +17122,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H249" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I249" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H249" s="5" t="n">
+        <v>8037000</v>
+      </c>
+      <c r="I249" s="5" t="n">
+        <v>22202</v>
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K249" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L249" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K249" s="5" t="n">
+        <v>7233300</v>
+      </c>
+      <c r="L249" s="5" t="n">
+        <v>19981</v>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N249" s="3" t="inlineStr">
@@ -18803,7 +18339,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>111</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -18818,7 +18354,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>152</t>
         </is>
       </c>
     </row>
@@ -19063,12 +18599,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K6" s="20" t="inlineStr">
+      <c r="K6" s="21" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
--
--
-(待售)</t>
+$686万
+$24,669/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
@@ -19166,12 +18702,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K7" s="20" t="inlineStr">
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
--
--
-(待售)</t>
+$678万
+$24,388/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -19269,12 +18805,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K8" s="20" t="inlineStr">
+      <c r="K8" s="21" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
--
--
-(待售)</t>
+$674万
+$24,245/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -19300,12 +18836,12 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
--
--
-(待售)</t>
+$1153万
+$27,584/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -19372,12 +18908,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K9" s="20" t="inlineStr">
+      <c r="K9" s="21" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
--
--
-(待售)</t>
+$670万
+$24,104/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -19388,12 +18924,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M9" s="20" t="inlineStr">
+      <c r="M9" s="21" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
--
--
-(待售)</t>
+$962万
+$24,920/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -19403,12 +18939,12 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
--
--
-(待售)</t>
+$1127万
+$26,957/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -19435,52 +18971,52 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
+$935万
+$25,823/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 387呎 (3房)
+$1038万
+$26,832/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$789万
+$24,880/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr">
-        <is>
-          <t>F | 387呎 (3房)
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I10" s="20" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J10" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K10" s="20" t="inlineStr">
+      <c r="K10" s="21" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
--
--
-(待售)</t>
+$666万
+$23,964/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -19491,12 +19027,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M10" s="20" t="inlineStr">
+      <c r="M10" s="21" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
--
--
-(待售)</t>
+$942万
+$24,417/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -19506,12 +19042,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
--
--
-(待售)</t>
+$1114万
+$26,653/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -19538,52 +19074,52 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
+$924万
+$25,522/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 387呎 (3房)
+$1026万
+$26,522/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$784万
+$24,735/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr">
-        <is>
-          <t>F | 387呎 (3房)
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I11" s="20" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J11" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K11" s="20" t="inlineStr">
+      <c r="K11" s="21" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
--
--
-(待售)</t>
+$662万
+$23,820/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -19594,12 +19130,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M11" s="20" t="inlineStr">
+      <c r="M11" s="21" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
--
--
-(待售)</t>
+$937万
+$24,277/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -19641,52 +19177,52 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
+$916万
+$25,296/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 387呎 (3房)
+$1017万
+$26,289/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$780万
+$24,593/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
-        <is>
-          <t>F | 387呎 (3房)
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I12" s="20" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J12" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K12" s="20" t="inlineStr">
+      <c r="K12" s="21" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
--
--
-(待售)</t>
+$658万
+$23,680/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -19744,52 +19280,52 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F13" s="20" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
+$910万
+$25,144/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 387呎 (2房)
+$1011万
+$26,132/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$775万
+$24,448/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="G13" s="20" t="inlineStr">
-        <is>
-          <t>F | 387呎 (2房)
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="H13" s="20" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I13" s="20" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J13" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K13" s="20" t="inlineStr">
+      <c r="K13" s="21" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
--
--
-(待售)</t>
+$654万
+$23,540/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -20021,12 +19557,12 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
--
--
-(待售)</t>
+$1095万
+$26,191/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -20053,52 +19589,52 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F16" s="20" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
+$894万
+$24,691/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 387呎 (2房)
+$993万
+$25,667/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="G16" s="20" t="inlineStr">
-        <is>
-          <t>F | 387呎 (2房)
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="H16" s="20" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="I16" s="20" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J16" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K16" s="20" t="inlineStr">
+      <c r="K16" s="21" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
--
--
-(待售)</t>
+$642万
+$23,101/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -20109,12 +19645,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M16" s="20" t="inlineStr">
+      <c r="M16" s="21" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
--
--
-(待售)</t>
+$923万
+$23,915/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -20124,12 +19660,12 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
--
--
-(待售)</t>
+$1073万
+$25,660/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -20156,52 +19692,52 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
+$888万
+$24,539/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 387呎 (2房)
+$987万
+$25,512/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$759万
+$23,946/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="G17" s="20" t="inlineStr">
-        <is>
-          <t>F | 387呎 (2房)
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="H17" s="20" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I17" s="20" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J17" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K17" s="20" t="inlineStr">
+      <c r="K17" s="21" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
--
--
-(待售)</t>
+$640万
+$23,014/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -20212,12 +19748,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M17" s="20" t="inlineStr">
+      <c r="M17" s="21" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
--
--
-(待售)</t>
+$907万
+$23,497/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -20259,28 +19795,28 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F18" s="20" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G18" s="20" t="inlineStr">
+$872万
+$24,086/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H18" s="20" t="inlineStr">
+$969万
+$25,047/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
--
--
-(待售)</t>
+$757万
+$23,874/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -20362,28 +19898,28 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G19" s="20" t="inlineStr">
+$847万
+$23,406/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H19" s="20" t="inlineStr">
+$942万
+$24,346/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
--
--
-(待售)</t>
+$754万
+$23,801/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -20465,28 +20001,28 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
+$851万
+$23,519/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 387呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="G20" s="20" t="inlineStr">
-        <is>
-          <t>F | 387呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H20" s="20" t="inlineStr">
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
--
--
-(待售)</t>
+$752万
+$23,729/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -20568,12 +20104,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F21" s="20" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
--
--
-(待售)</t>
+$846万
+$23,367/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -20671,28 +20207,28 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F22" s="20" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G22" s="20" t="inlineStr">
+$828万
+$22,878/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H22" s="20" t="inlineStr">
+$921万
+$23,804/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
--
--
-(待售)</t>
+$748万
+$23,587/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -20774,28 +20310,28 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F23" s="20" t="inlineStr">
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G23" s="20" t="inlineStr">
+$828万
+$22,878/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H23" s="20" t="inlineStr">
+$921万
+$23,804/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
--
--
-(待售)</t>
+$745万
+$23,514/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -20877,28 +20413,28 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F24" s="20" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G24" s="20" t="inlineStr">
+$817万
+$22,577/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H24" s="20" t="inlineStr">
+$909万
+$23,494/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
--
--
-(待售)</t>
+$745万
+$23,514/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -20980,28 +20516,28 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G25" s="20" t="inlineStr">
+$804万
+$22,202/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H25" s="20" t="inlineStr">
+$897万
+$23,183/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
--
--
-(待售)</t>
+$742万
+$23,407/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">

--- a/files/九龙-红磡-映汇.xlsx
+++ b/files/九龙-红磡-映汇.xlsx
@@ -116,12 +116,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
+      <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -260,10 +261,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1108,7 +1109,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1118,12 +1119,12 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1133,12 +1134,12 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1148,7 +1149,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1249,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1450,7 +1451,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1460,12 +1461,12 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1475,12 +1476,12 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1490,7 +1491,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1591,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1652,7 +1653,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1784,7 +1785,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -1792,34 +1793,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H18" s="5" t="n">
+        <v>6871000</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>26027</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>6183900</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>23424</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2064,7 +2057,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -2406,7 +2399,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2468,7 +2461,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -2600,7 +2593,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -2608,34 +2601,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H30" s="5" t="n">
+        <v>6791000</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>25723</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>6111900</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>23151</v>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -2880,7 +2865,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -3222,7 +3207,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -3284,7 +3269,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -3416,7 +3401,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -3424,34 +3409,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H42" s="5" t="n">
+        <v>6752000</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>25576</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>6076800</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>23018</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -3556,7 +3533,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -3564,34 +3541,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H44" s="5" t="n">
+        <v>10666000</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>27561</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>9599400</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>24805</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -3696,7 +3665,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -3968,7 +3937,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -4030,7 +3999,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -4092,7 +4061,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -4224,7 +4193,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -4232,34 +4201,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H54" s="5" t="n">
+        <v>6712000</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>25424</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K54" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L54" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>6040800</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>22882</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -4364,7 +4325,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -4372,34 +4333,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H56" s="5" t="n">
+        <v>10575000</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>27326</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K56" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L56" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>9517500</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>24593</v>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
@@ -4504,7 +4457,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -4706,7 +4659,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -4768,7 +4721,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -4830,7 +4783,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -4892,7 +4845,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -5024,7 +4977,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -5032,34 +4985,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H66" s="5" t="n">
+        <v>6672000</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>25273</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K66" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L66" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>6004800</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>22745</v>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
@@ -5094,7 +5039,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -5156,7 +5101,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -5218,7 +5163,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -5280,7 +5225,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -5482,7 +5427,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -5544,7 +5489,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -5606,7 +5551,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -5668,7 +5613,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -5800,7 +5745,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -5808,34 +5753,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I78" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H78" s="5" t="n">
+        <v>6633000</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>25125</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K78" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L78" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>5969700</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>22612</v>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
@@ -5870,7 +5807,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -5932,7 +5869,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -5994,7 +5931,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -6056,7 +5993,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
@@ -6258,7 +6195,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -6320,7 +6257,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
@@ -6382,7 +6319,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
@@ -6444,7 +6381,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -6576,7 +6513,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
@@ -6584,34 +6521,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I90" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H90" s="5" t="n">
+        <v>6593000</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>24973</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K90" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L90" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>5933700</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>22476</v>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
@@ -6646,7 +6575,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -6708,7 +6637,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
@@ -6770,7 +6699,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -6832,7 +6761,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
@@ -7034,7 +6963,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
@@ -7096,7 +7025,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
@@ -7158,7 +7087,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -7220,7 +7149,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
@@ -7352,7 +7281,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
@@ -7360,34 +7289,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I102" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H102" s="5" t="n">
+        <v>6551000</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>24814</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K102" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L102" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>5895900</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>22333</v>
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N102" s="3" t="inlineStr">
@@ -7422,7 +7343,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
@@ -7484,7 +7405,7 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
@@ -7546,7 +7467,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -7608,7 +7529,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -7810,7 +7731,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
@@ -7942,7 +7863,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -8144,7 +8065,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
@@ -8152,34 +8073,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I114" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H114" s="5" t="n">
+        <v>6520000</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>24697</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K114" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L114" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>5868000</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>22227</v>
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N114" s="3" t="inlineStr">
@@ -8214,7 +8127,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
@@ -8222,34 +8135,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H115" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I115" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H115" s="5" t="n">
+        <v>7893000</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>24899</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K115" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L115" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>7103700</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>22409</v>
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N115" s="3" t="inlineStr">
@@ -8354,7 +8259,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
@@ -8362,34 +8267,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H117" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I117" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H117" s="5" t="n">
+        <v>9268000</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>25602</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K117" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L117" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>8341200</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>23042</v>
       </c>
       <c r="M117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N117" s="3" t="inlineStr">
@@ -8424,7 +8321,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
@@ -8766,7 +8663,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
@@ -8968,7 +8865,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -8976,34 +8873,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H126" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I126" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H126" s="5" t="n">
+        <v>6520000</v>
+      </c>
+      <c r="I126" s="5" t="n">
+        <v>24697</v>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K126" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L126" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>5868000</v>
+      </c>
+      <c r="L126" s="5" t="n">
+        <v>22227</v>
       </c>
       <c r="M126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N126" s="3" t="inlineStr">
@@ -9038,7 +8927,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
@@ -9046,34 +8935,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H127" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I127" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H127" s="5" t="n">
+        <v>7893000</v>
+      </c>
+      <c r="I127" s="5" t="n">
+        <v>24899</v>
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K127" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L127" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>7103700</v>
+      </c>
+      <c r="L127" s="5" t="n">
+        <v>22409</v>
       </c>
       <c r="M127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N127" s="3" t="inlineStr">
@@ -9108,7 +8989,7 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
@@ -9116,34 +8997,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I128" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H128" s="5" t="n">
+        <v>10150000</v>
+      </c>
+      <c r="I128" s="5" t="n">
+        <v>26227</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K128" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L128" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>9135000</v>
+      </c>
+      <c r="L128" s="5" t="n">
+        <v>23605</v>
       </c>
       <c r="M128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N128" s="3" t="inlineStr">
@@ -9178,7 +9051,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
@@ -9186,34 +9059,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H129" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I129" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H129" s="5" t="n">
+        <v>9268000</v>
+      </c>
+      <c r="I129" s="5" t="n">
+        <v>25602</v>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K129" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L129" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>8341200</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>23042</v>
       </c>
       <c r="M129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N129" s="3" t="inlineStr">
@@ -9248,7 +9113,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
@@ -9520,7 +9385,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
@@ -9582,7 +9447,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
@@ -9644,7 +9509,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -9846,7 +9711,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
@@ -9854,34 +9719,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H139" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I139" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H139" s="5" t="n">
+        <v>7799000</v>
+      </c>
+      <c r="I139" s="5" t="n">
+        <v>24603</v>
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K139" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L139" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="n">
+        <v>7019100</v>
+      </c>
+      <c r="L139" s="5" t="n">
+        <v>22142</v>
       </c>
       <c r="M139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N139" s="3" t="inlineStr">
@@ -9916,7 +9773,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -9978,7 +9835,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -10040,7 +9897,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
@@ -10242,7 +10099,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
@@ -10304,7 +10161,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
@@ -10366,7 +10223,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
@@ -10428,7 +10285,7 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
@@ -10630,7 +10487,7 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
@@ -10692,7 +10549,7 @@
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
@@ -10754,7 +10611,7 @@
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
@@ -10816,7 +10673,7 @@
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
@@ -11018,7 +10875,7 @@
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
@@ -11080,7 +10937,7 @@
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
@@ -11142,7 +10999,7 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
@@ -11414,7 +11271,7 @@
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
@@ -11476,7 +11333,7 @@
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
@@ -11538,7 +11395,7 @@
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
@@ -11600,7 +11457,7 @@
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
@@ -11802,7 +11659,7 @@
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
@@ -11864,7 +11721,7 @@
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
@@ -11926,7 +11783,7 @@
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
@@ -12198,7 +12055,7 @@
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
@@ -12260,7 +12117,7 @@
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
@@ -12322,7 +12179,7 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
@@ -12384,7 +12241,7 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
@@ -12516,7 +12373,7 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
@@ -12524,34 +12381,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H180" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I180" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H180" s="5" t="n">
+        <v>8831000</v>
+      </c>
+      <c r="I180" s="5" t="n">
+        <v>24328</v>
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K180" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L180" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K180" s="5" t="n">
+        <v>7947900</v>
+      </c>
+      <c r="L180" s="5" t="n">
+        <v>21895</v>
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N180" s="3" t="inlineStr">
@@ -12586,7 +12435,7 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
@@ -12718,7 +12567,7 @@
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
@@ -12990,7 +12839,7 @@
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
@@ -13052,7 +12901,7 @@
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
@@ -13060,34 +12909,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H188" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I188" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H188" s="5" t="n">
+        <v>9422000</v>
+      </c>
+      <c r="I188" s="5" t="n">
+        <v>24346</v>
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K188" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L188" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K188" s="5" t="n">
+        <v>8479800</v>
+      </c>
+      <c r="L188" s="5" t="n">
+        <v>21912</v>
       </c>
       <c r="M188" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N188" s="3" t="inlineStr">
@@ -13122,7 +12963,7 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
@@ -13184,7 +13025,7 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
@@ -13316,7 +13157,7 @@
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
@@ -13324,34 +13165,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H192" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I192" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H192" s="5" t="n">
+        <v>8747000</v>
+      </c>
+      <c r="I192" s="5" t="n">
+        <v>24096</v>
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K192" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L192" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K192" s="5" t="n">
+        <v>7872300</v>
+      </c>
+      <c r="L192" s="5" t="n">
+        <v>21687</v>
       </c>
       <c r="M192" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N192" s="3" t="inlineStr">
@@ -13526,7 +13359,7 @@
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
@@ -13798,7 +13631,7 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
@@ -13806,34 +13639,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H199" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I199" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H199" s="5" t="n">
+        <v>7683000</v>
+      </c>
+      <c r="I199" s="5" t="n">
+        <v>24237</v>
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K199" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L199" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K199" s="5" t="n">
+        <v>6914700</v>
+      </c>
+      <c r="L199" s="5" t="n">
+        <v>21813</v>
       </c>
       <c r="M199" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N199" s="3" t="inlineStr">
@@ -13938,7 +13763,7 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -14000,7 +13825,7 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
@@ -14132,7 +13957,7 @@
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
@@ -14140,34 +13965,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H204" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I204" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H204" s="5" t="n">
+        <v>8691000</v>
+      </c>
+      <c r="I204" s="5" t="n">
+        <v>23942</v>
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K204" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L204" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K204" s="5" t="n">
+        <v>7821900</v>
+      </c>
+      <c r="L204" s="5" t="n">
+        <v>21548</v>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N204" s="3" t="inlineStr">
@@ -14342,7 +14159,7 @@
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
@@ -14614,7 +14431,7 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -14676,7 +14493,7 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -14738,7 +14555,7 @@
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -14800,7 +14617,7 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -14932,7 +14749,7 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -14940,34 +14757,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H216" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I216" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H216" s="5" t="n">
+        <v>8635000</v>
+      </c>
+      <c r="I216" s="5" t="n">
+        <v>23788</v>
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K216" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L216" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K216" s="5" t="n">
+        <v>7771500</v>
+      </c>
+      <c r="L216" s="5" t="n">
+        <v>21409</v>
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N216" s="3" t="inlineStr">
@@ -15142,7 +14951,7 @@
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
@@ -15414,7 +15223,7 @@
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
@@ -15476,7 +15285,7 @@
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -15538,7 +15347,7 @@
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
@@ -15600,7 +15409,7 @@
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -15732,7 +15541,7 @@
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
@@ -15740,34 +15549,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H228" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I228" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H228" s="5" t="n">
+        <v>8635000</v>
+      </c>
+      <c r="I228" s="5" t="n">
+        <v>23788</v>
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K228" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L228" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K228" s="5" t="n">
+        <v>7771500</v>
+      </c>
+      <c r="L228" s="5" t="n">
+        <v>21409</v>
       </c>
       <c r="M228" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N228" s="3" t="inlineStr">
@@ -15872,7 +15673,7 @@
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
@@ -15934,7 +15735,7 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -16206,7 +16007,7 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
@@ -16268,7 +16069,7 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
@@ -16330,7 +16131,7 @@
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
@@ -16392,7 +16193,7 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -16524,7 +16325,7 @@
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -16532,34 +16333,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H240" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I240" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H240" s="5" t="n">
+        <v>8523000</v>
+      </c>
+      <c r="I240" s="5" t="n">
+        <v>23479</v>
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K240" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L240" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K240" s="5" t="n">
+        <v>7670700</v>
+      </c>
+      <c r="L240" s="5" t="n">
+        <v>21131</v>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N240" s="3" t="inlineStr">
@@ -16594,7 +16387,7 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -16656,7 +16449,7 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -16718,7 +16511,7 @@
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -16990,7 +16783,7 @@
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
@@ -17052,7 +16845,7 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -17114,7 +16907,7 @@
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
@@ -17176,7 +16969,7 @@
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -17308,7 +17101,7 @@
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
@@ -17316,34 +17109,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H252" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I252" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H252" s="5" t="n">
+        <v>8425000</v>
+      </c>
+      <c r="I252" s="5" t="n">
+        <v>23209</v>
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K252" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L252" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K252" s="5" t="n">
+        <v>7582500</v>
+      </c>
+      <c r="L252" s="5" t="n">
+        <v>20888</v>
       </c>
       <c r="M252" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N252" s="3" t="inlineStr">
@@ -17378,7 +17163,7 @@
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
@@ -17440,7 +17225,7 @@
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -17450,12 +17235,12 @@
       </c>
       <c r="H254" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I254" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J254" s="3" t="inlineStr">
@@ -17465,12 +17250,12 @@
       </c>
       <c r="K254" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L254" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M254" s="3" t="inlineStr">
@@ -17480,7 +17265,7 @@
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -17860,7 +17645,7 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -17870,12 +17655,12 @@
       </c>
       <c r="H260" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I260" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J260" s="3" t="inlineStr">
@@ -17885,12 +17670,12 @@
       </c>
       <c r="K260" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L260" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M260" s="3" t="inlineStr">
@@ -17900,7 +17685,7 @@
       </c>
       <c r="N260" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -18210,7 +17995,7 @@
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
@@ -18220,12 +18005,12 @@
       </c>
       <c r="H265" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I265" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J265" s="3" t="inlineStr">
@@ -18235,12 +18020,12 @@
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L265" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M265" s="3" t="inlineStr">
@@ -18250,7 +18035,7 @@
       </c>
       <c r="N265" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -18334,14 +18119,14 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
           <t>0</t>
@@ -18354,7 +18139,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>120</t>
         </is>
       </c>
     </row>
@@ -18434,36 +18219,36 @@
       <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 630呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 357呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>B | 357呎 (2房)
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
 $969万
 $27,137/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
 -
@@ -18474,44 +18259,44 @@
       <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 387呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="H5" s="20" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="I5" s="20" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="J5" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
+      <c r="K5" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="K5" s="20" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="L5" s="20" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
 -
@@ -18527,7 +18312,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 -
@@ -18535,7 +18320,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
 -
@@ -18543,7 +18328,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
 -
@@ -18551,15 +18336,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
 $941万
 $26,347/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
 -
@@ -18567,7 +18352,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>F | 387呎 (3房)
 -
@@ -18575,7 +18360,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
 -
@@ -18586,36 +18371,36 @@
       <c r="I6" s="20" t="inlineStr">
         <is>
           <t>H | 264呎 (1房)
+$687万
+$26,027/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="J6" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K6" s="21" t="inlineStr">
+      <c r="K6" s="20" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
 $686万
 $24,669/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L6" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
 $660万
 $24,539/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M6" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M6" s="21" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 -
@@ -18630,7 +18415,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 -
@@ -18638,7 +18423,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
 -
@@ -18646,7 +18431,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
 -
@@ -18654,15 +18439,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
 $925万
 $25,916/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F7" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
 -
@@ -18670,7 +18455,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 387呎 (3房)
 -
@@ -18678,7 +18463,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
 -
@@ -18689,36 +18474,36 @@
       <c r="I7" s="20" t="inlineStr">
         <is>
           <t>H | 264呎 (1房)
+$679万
+$25,723/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="J7" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K7" s="21" t="inlineStr">
+      <c r="K7" s="20" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
 $678万
 $24,388/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L7" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
 $653万
 $24,260/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M7" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M7" s="21" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 -
@@ -18733,7 +18518,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 -
@@ -18741,7 +18526,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
 -
@@ -18749,7 +18534,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
 -
@@ -18757,15 +18542,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
 $918万
 $25,703/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
 -
@@ -18776,52 +18561,52 @@
       <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 387呎 (3房)
+$1067万
+$27,561/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$675万
+$25,576/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J8" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K8" s="21" t="inlineStr">
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
 $674万
 $24,245/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L8" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
 $649万
 $24,119/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M8" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M8" s="21" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 -
@@ -18836,15 +18621,15 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 $1153万
 $27,584/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
 -
@@ -18852,7 +18637,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
 -
@@ -18860,15 +18645,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
 $910万
 $25,487/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
 -
@@ -18879,57 +18664,57 @@
       <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 387呎 (3房)
+$1058万
+$27,326/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$671万
+$25,424/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J9" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K9" s="21" t="inlineStr">
+      <c r="K9" s="20" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
 $670万
 $24,104/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L9" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="L9" s="20" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
 $645万
 $23,978/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M9" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M9" s="20" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 $962万
 $24,920/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -18939,15 +18724,15 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 $1127万
 $26,957/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
 -
@@ -18955,7 +18740,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
 -
@@ -18963,76 +18748,76 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
 $902万
 $25,272/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
 $935万
 $25,823/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G10" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 387呎 (3房)
 $1038万
 $26,832/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
 $789万
 $24,880/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
         <is>
           <t>H | 264呎 (1房)
+$667万
+$25,273/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="J10" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K10" s="21" t="inlineStr">
+      <c r="K10" s="20" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
 $666万
 $23,964/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L10" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
 $641万
 $23,836/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M10" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M10" s="20" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 $942万
 $24,417/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -19042,15 +18827,15 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 $1114万
 $26,653/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
 -
@@ -19058,7 +18843,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
 -
@@ -19066,76 +18851,76 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
 $892万
 $24,986/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
 $924万
 $25,522/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G11" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 387呎 (3房)
 $1026万
 $26,522/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H11" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
 $784万
 $24,735/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
         <is>
           <t>H | 264呎 (1房)
+$663万
+$25,125/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="J11" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K11" s="21" t="inlineStr">
+      <c r="K11" s="20" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
 $662万
 $23,820/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L11" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
 $637万
 $23,695/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M11" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M11" s="20" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 $937万
 $24,277/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -19145,15 +18930,15 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 $1078万
 $25,780/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
 -
@@ -19161,7 +18946,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
 -
@@ -19169,76 +18954,76 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
 $884万
 $24,770/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F12" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
 $916万
 $25,296/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G12" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 387呎 (3房)
 $1017万
 $26,289/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H12" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
 $780万
 $24,593/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
         <is>
           <t>H | 264呎 (1房)
+$659万
+$24,973/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="J12" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K12" s="21" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
 $658万
 $23,680/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L12" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
 $634万
 $23,558/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M12" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M12" s="20" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 $909万
 $23,547/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -19248,15 +19033,15 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 $1071万
 $25,629/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
 -
@@ -19264,7 +19049,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
 -
@@ -19272,76 +19057,76 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
 $879万
 $24,627/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F13" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
 $910万
 $25,144/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G13" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
 $1011万
 $26,132/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H13" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
 $775万
 $24,448/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
         <is>
           <t>H | 264呎 (1房)
+$655万
+$24,814/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="J13" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K13" s="21" t="inlineStr">
+      <c r="K13" s="20" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
 $654万
 $23,540/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L13" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
 $630万
 $23,416/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M13" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M13" s="20" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 $904万
 $23,409/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -19351,7 +19136,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 -
@@ -19359,7 +19144,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
 -
@@ -19367,7 +19152,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
 -
@@ -19375,71 +19160,71 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
 $874万
 $24,485/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
+$927万
+$25,602/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 387呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="G14" s="20" t="inlineStr">
-        <is>
-          <t>F | 387呎 (2房)
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$789万
+$24,899/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$652万
+$24,697/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
+      <c r="K14" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="I14" s="20" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J14" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K14" s="20" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="L14" s="21" t="inlineStr">
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
 $626万
 $23,275/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M14" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M14" s="21" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 -
@@ -19454,7 +19239,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 -
@@ -19462,7 +19247,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
 -
@@ -19470,7 +19255,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
 -
@@ -19478,71 +19263,71 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
 $874万
 $24,485/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
+$927万
+$25,602/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 387呎 (2房)
+$1015万
+$26,227/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$789万
+$24,899/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$652万
+$24,697/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="G15" s="20" t="inlineStr">
-        <is>
-          <t>F | 387呎 (2房)
+      <c r="K15" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="H15" s="20" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I15" s="20" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J15" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K15" s="20" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="L15" s="21" t="inlineStr">
+      <c r="L15" s="20" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
 $626万
 $23,275/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M15" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M15" s="21" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 -
@@ -19557,15 +19342,15 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 $1095万
 $26,191/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
 -
@@ -19573,7 +19358,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
 -
@@ -19581,76 +19366,76 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
 $864万
 $24,199/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
 $894万
 $24,691/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G16" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
 $993万
 $25,667/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
+$780万
+$24,603/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="I16" s="20" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
+      <c r="J16" s="21" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="J16" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K16" s="21" t="inlineStr">
+      <c r="K16" s="20" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
 $642万
 $23,101/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L16" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="L16" s="20" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
 $619万
 $22,996/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M16" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M16" s="20" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 $923万
 $23,915/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -19660,15 +19445,15 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 $1073万
 $25,660/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
 -
@@ -19676,7 +19461,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
 -
@@ -19684,39 +19469,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
 $859万
 $24,056/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F17" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
 $888万
 $24,539/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G17" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
 $987万
 $25,512/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H17" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
 $759万
 $23,946/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I17" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
         <is>
           <t>H | 264呎 (1房)
 -
@@ -19724,7 +19509,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J17" s="20" t="inlineStr">
+      <c r="J17" s="21" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 -
@@ -19732,28 +19517,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K17" s="21" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
 $640万
 $23,014/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L17" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
 $617万
 $22,926/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M17" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M17" s="20" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 $907万
 $23,497/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -19763,15 +19548,15 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 $1028万
 $24,589/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
 -
@@ -19779,7 +19564,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
 -
@@ -19787,39 +19572,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
 $843万
 $23,625/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
 $872万
 $24,086/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G18" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
 $969万
 $25,047/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H18" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
 $757万
 $23,874/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I18" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
         <is>
           <t>H | 264呎 (1房)
 -
@@ -19827,7 +19612,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J18" s="20" t="inlineStr">
+      <c r="J18" s="21" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 -
@@ -19835,7 +19620,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K18" s="20" t="inlineStr">
+      <c r="K18" s="21" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
 -
@@ -19843,20 +19628,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L18" s="21" t="inlineStr">
+      <c r="L18" s="20" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
 $615万
 $22,855/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M18" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M18" s="20" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 $882万
 $22,855/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -19866,63 +19651,63 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 $1000万
 $23,919/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
+$883万
+$24,328/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
 $820万
 $22,980/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F19" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
 $847万
 $23,406/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G19" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
 $942万
 $24,346/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H19" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
 $754万
 $23,801/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I19" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>H | 264呎 (1房)
 -
@@ -19930,7 +19715,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J19" s="20" t="inlineStr">
+      <c r="J19" s="21" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 -
@@ -19938,7 +19723,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K19" s="20" t="inlineStr">
+      <c r="K19" s="21" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
 -
@@ -19946,20 +19731,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L19" s="21" t="inlineStr">
+      <c r="L19" s="20" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
 $613万
 $22,784/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M19" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M19" s="20" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 $880万
 $22,788/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -19969,7 +19754,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 -
@@ -19980,52 +19765,52 @@
       <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
+$875万
+$24,096/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
 $813万
 $22,768/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F20" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
 $851万
 $23,519/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H20" s="21" t="inlineStr">
+$942万
+$24,346/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
 $752万
 $23,729/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I20" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>H | 264呎 (1房)
 -
@@ -20033,7 +19818,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J20" s="20" t="inlineStr">
+      <c r="J20" s="21" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 -
@@ -20041,7 +19826,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K20" s="20" t="inlineStr">
+      <c r="K20" s="21" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
 -
@@ -20049,15 +19834,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L20" s="21" t="inlineStr">
+      <c r="L20" s="20" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
 $611万
 $22,714/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M20" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M20" s="21" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 -
@@ -20072,7 +19857,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 -
@@ -20083,36 +19868,36 @@
       <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
+$869万
+$23,942/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
 $808万
 $22,625/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F21" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
 $846万
 $23,367/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G21" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
 -
@@ -20123,44 +19908,44 @@
       <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
+$768万
+$24,237/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="I21" s="20" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
+      <c r="J21" s="21" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="J21" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
+      <c r="K21" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="K21" s="20" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="L21" s="21" t="inlineStr">
+      <c r="L21" s="20" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
 $609万
 $22,643/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M21" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M21" s="21" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 -
@@ -20175,7 +19960,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 -
@@ -20186,52 +19971,52 @@
       <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
+$864万
+$23,788/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
 $803万
 $22,482/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
 $828万
 $22,878/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
 $921万
 $23,804/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H22" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
 $748万
 $23,587/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I22" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
         <is>
           <t>H | 264呎 (1房)
 -
@@ -20239,7 +20024,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J22" s="20" t="inlineStr">
+      <c r="J22" s="21" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 -
@@ -20247,7 +20032,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K22" s="20" t="inlineStr">
+      <c r="K22" s="21" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
 -
@@ -20255,15 +20040,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L22" s="21" t="inlineStr">
+      <c r="L22" s="20" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
 $607万
 $22,572/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M22" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M22" s="21" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 -
@@ -20278,7 +20063,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 -
@@ -20289,52 +20074,52 @@
       <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
+$864万
+$23,788/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D23" s="20" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
 $803万
 $22,482/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F23" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
 $828万
 $22,878/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G23" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
 $921万
 $23,804/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H23" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
 $745万
 $23,514/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I23" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
         <is>
           <t>H | 264呎 (1房)
 -
@@ -20342,7 +20127,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J23" s="20" t="inlineStr">
+      <c r="J23" s="21" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 -
@@ -20350,7 +20135,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K23" s="20" t="inlineStr">
+      <c r="K23" s="21" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
 -
@@ -20358,15 +20143,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L23" s="21" t="inlineStr">
+      <c r="L23" s="20" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
 $605万
 $22,502/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M23" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M23" s="21" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 -
@@ -20381,63 +20166,63 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 $966万
 $23,100/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
+$852万
+$23,479/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
 $792万
 $22,193/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
 $817万
 $22,577/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
 $909万
 $23,494/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H24" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
 $745万
 $23,514/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I24" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
         <is>
           <t>H | 264呎 (1房)
 -
@@ -20445,7 +20230,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J24" s="20" t="inlineStr">
+      <c r="J24" s="21" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 -
@@ -20453,7 +20238,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K24" s="20" t="inlineStr">
+      <c r="K24" s="21" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
 -
@@ -20461,20 +20246,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L24" s="21" t="inlineStr">
+      <c r="L24" s="20" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
 $605万
 $22,502/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M24" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M24" s="20" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 $869万
 $22,510/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -20484,63 +20269,63 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 $953万
 $22,801/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
+$842万
+$23,209/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
 $783万
 $21,924/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
 $804万
 $22,202/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
 $897万
 $23,183/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
 $742万
 $23,407/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I25" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
         <is>
           <t>H | 264呎 (1房)
 -
@@ -20548,7 +20333,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J25" s="20" t="inlineStr">
+      <c r="J25" s="21" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 -
@@ -20556,7 +20341,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K25" s="20" t="inlineStr">
+      <c r="K25" s="21" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
 -
@@ -20564,20 +20349,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L25" s="21" t="inlineStr">
+      <c r="L25" s="20" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
 $603万
 $22,424/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M25" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M25" s="20" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 $866万
 $22,440/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -20590,97 +20375,97 @@
       <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 380呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 325呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>B | 325呎 (2房)
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 320呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>C | 320呎 (2房)
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 319呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E26" s="20" t="inlineStr">
-        <is>
-          <t>D | 319呎 (2房)
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>E | 324呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="F26" s="20" t="inlineStr">
-        <is>
-          <t>E | 324呎 (2房)
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 350呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>G | 280呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="G26" s="20" t="inlineStr">
-        <is>
-          <t>F | 350呎 (2房)
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>H | 226呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="H26" s="20" t="inlineStr">
-        <is>
-          <t>G | 280呎 (1房)
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>J | 306呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="I26" s="20" t="inlineStr">
-        <is>
-          <t>H | 226呎 (1房)
+      <c r="K26" s="21" t="inlineStr">
+        <is>
+          <t>K | 240呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="J26" s="20" t="inlineStr">
-        <is>
-          <t>J | 306呎 (2房)
+      <c r="L26" s="21" t="inlineStr">
+        <is>
+          <t>L | 231呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="K26" s="20" t="inlineStr">
-        <is>
-          <t>K | 240呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="L26" s="20" t="inlineStr">
-        <is>
-          <t>L | 231呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="M26" s="20" t="inlineStr">
         <is>
           <t>M | 348呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-红磡-映汇.xlsx
+++ b/files/九龙-红磡-映汇.xlsx
@@ -127,12 +127,12 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
+      <color rgb="00660000"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
+      <color rgb="00002060"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -277,13 +277,13 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -666,7 +666,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1537,34 +1537,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H14" s="5" t="n">
+        <v>10314000</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>26720</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>9282600</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>24048</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1723,7 +1715,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1731,34 +1723,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H17" s="5" t="n">
+        <v>8905000</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>25887</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>8014500</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>23298</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -1925,7 +1909,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1933,34 +1917,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H20" s="5" t="n">
+        <v>11355000</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>29341</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>10219500</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>26407</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -2127,7 +2103,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -2154,7 +2130,7 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -2259,7 +2235,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -2267,34 +2243,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H25" s="5" t="n">
+        <v>12491000</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>29883</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>11241900</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>26894</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -2329,7 +2297,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -2337,34 +2305,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H26" s="5" t="n">
+        <v>10198000</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>26420</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>9178200</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>23778</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -2523,7 +2483,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2531,34 +2491,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H29" s="5" t="n">
+        <v>8804000</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>25593</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>7923600</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>23034</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -2725,7 +2677,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -2733,34 +2685,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H32" s="5" t="n">
+        <v>11166000</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>28853</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>10049400</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>25967</v>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -2927,7 +2871,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2954,7 +2898,7 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -3059,7 +3003,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -3067,34 +3011,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H37" s="5" t="n">
+        <v>12288000</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>29397</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>11059200</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>26457</v>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -3129,7 +3065,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -3137,34 +3073,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H38" s="5" t="n">
+        <v>10139000</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>26267</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>9125100</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>23640</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -3323,7 +3251,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -3331,34 +3259,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H41" s="5" t="n">
+        <v>8753000</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>25445</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>7877700</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>22900</v>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
@@ -3719,23 +3639,23 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
-        <v>9932000</v>
+        <v>8938800</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>27743</v>
+        <v>24969</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="5" t="n">
@@ -3746,7 +3666,7 @@
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
@@ -3851,7 +3771,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -3859,34 +3779,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H49" s="5" t="n">
+        <v>12186000</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>29153</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L49" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>10967400</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>26238</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
@@ -4107,7 +4019,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -4115,34 +4027,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H53" s="5" t="n">
+        <v>8702000</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>25297</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>7831800</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>22767</v>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -4503,7 +4407,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -4530,7 +4434,7 @@
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
@@ -4883,7 +4787,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -4891,34 +4795,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H65" s="5" t="n">
+        <v>8651000</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>25148</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K65" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L65" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>7785900</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>22633</v>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
@@ -5263,23 +5159,23 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
-        <v>9767000</v>
+        <v>8790300</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>27282</v>
+        <v>24554</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="5" t="n">
@@ -5290,7 +5186,7 @@
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr">
@@ -5643,7 +5539,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -5651,34 +5547,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H77" s="5" t="n">
+        <v>8600000</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>25000</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K77" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L77" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>7740000</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>22500</v>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
@@ -6023,34 +5911,34 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
-        <v>9657000</v>
+        <v>8787800</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>26975</v>
+        <v>24547</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="5" t="n">
-        <v>8691300</v>
+        <v>8787800</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>24277</v>
+        <v>24547</v>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
@@ -6403,7 +6291,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
@@ -6411,34 +6299,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I89" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H89" s="5" t="n">
+        <v>8549000</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>24852</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K89" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L89" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>7694100</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>22367</v>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N89" s="3" t="inlineStr">
@@ -6783,23 +6663,23 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
-        <v>9575000</v>
+        <v>8617500</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>26746</v>
+        <v>24071</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K95" s="5" t="n">
@@ -6810,7 +6690,7 @@
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N95" s="3" t="inlineStr">
@@ -7163,7 +7043,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -7171,34 +7051,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I101" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H101" s="5" t="n">
+        <v>8498000</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>24703</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K101" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L101" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>7648200</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>22233</v>
       </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N101" s="3" t="inlineStr">
@@ -7543,23 +7415,23 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
-        <v>9520000</v>
+        <v>8568000</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>26592</v>
+        <v>23933</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K107" s="5" t="n">
@@ -7570,7 +7442,7 @@
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N107" s="3" t="inlineStr">
@@ -7737,7 +7609,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
@@ -7764,7 +7636,7 @@
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N110" s="3" t="inlineStr">
@@ -7861,34 +7733,34 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
-        <v>6724000</v>
+        <v>6118800</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>24187</v>
+        <v>22010</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K112" s="5" t="n">
-        <v>6051600</v>
+        <v>6118800</v>
       </c>
       <c r="L112" s="5" t="n">
-        <v>21768</v>
+        <v>22010</v>
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N112" s="3" t="inlineStr">
@@ -7923,7 +7795,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -7931,34 +7803,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H113" s="5" t="n">
+        <v>8448000</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>24558</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>7603200</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>22102</v>
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N113" s="3" t="inlineStr">
@@ -8117,34 +7981,34 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
-        <v>10392000</v>
+        <v>9456700</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>26853</v>
+        <v>24436</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K116" s="5" t="n">
-        <v>9352800</v>
+        <v>9456700</v>
       </c>
       <c r="L116" s="5" t="n">
-        <v>24167</v>
+        <v>24436</v>
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N116" s="3" t="inlineStr">
@@ -8303,23 +8167,23 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
-        <v>9465000</v>
+        <v>8518500</v>
       </c>
       <c r="I119" s="5" t="n">
-        <v>26439</v>
+        <v>23795</v>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K119" s="5" t="n">
@@ -8330,7 +8194,7 @@
       </c>
       <c r="M119" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N119" s="3" t="inlineStr">
@@ -8435,23 +8299,23 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
-        <v>11450000</v>
+        <v>10305000</v>
       </c>
       <c r="I121" s="5" t="n">
-        <v>27392</v>
+        <v>24653</v>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K121" s="5" t="n">
@@ -8462,7 +8326,7 @@
       </c>
       <c r="M121" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N121" s="3" t="inlineStr">
@@ -8497,7 +8361,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
@@ -8524,7 +8388,7 @@
       </c>
       <c r="M122" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N122" s="3" t="inlineStr">
@@ -8621,34 +8485,34 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
-        <v>6724000</v>
+        <v>6186000</v>
       </c>
       <c r="I124" s="5" t="n">
-        <v>24187</v>
+        <v>22252</v>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K124" s="5" t="n">
-        <v>6051600</v>
+        <v>6186000</v>
       </c>
       <c r="L124" s="5" t="n">
-        <v>21768</v>
+        <v>22252</v>
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N124" s="3" t="inlineStr">
@@ -8683,7 +8547,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
@@ -8691,34 +8555,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H125" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I125" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H125" s="5" t="n">
+        <v>8448000</v>
+      </c>
+      <c r="I125" s="5" t="n">
+        <v>24558</v>
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K125" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L125" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>7603200</v>
+      </c>
+      <c r="L125" s="5" t="n">
+        <v>22102</v>
       </c>
       <c r="M125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N125" s="3" t="inlineStr">
@@ -8842,7 +8698,7 @@
       </c>
       <c r="M127" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N127" s="3" t="inlineStr">
@@ -9063,23 +8919,23 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
-        <v>9465000</v>
+        <v>8518500</v>
       </c>
       <c r="I131" s="5" t="n">
-        <v>26439</v>
+        <v>23795</v>
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K131" s="5" t="n">
@@ -9090,7 +8946,7 @@
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N131" s="3" t="inlineStr">
@@ -9195,23 +9051,23 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
-        <v>11450000</v>
+        <v>10305000</v>
       </c>
       <c r="I133" s="5" t="n">
-        <v>27392</v>
+        <v>24653</v>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K133" s="5" t="n">
@@ -9222,7 +9078,7 @@
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N133" s="3" t="inlineStr">
@@ -9443,7 +9299,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
@@ -9451,34 +9307,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H137" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I137" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H137" s="5" t="n">
+        <v>8346000</v>
+      </c>
+      <c r="I137" s="5" t="n">
+        <v>24262</v>
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K137" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L137" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>7511400</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>21835</v>
       </c>
       <c r="M137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N137" s="3" t="inlineStr">
@@ -9513,23 +9361,23 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
-        <v>6587000</v>
+        <v>5928300</v>
       </c>
       <c r="I138" s="5" t="n">
-        <v>24951</v>
+        <v>22456</v>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K138" s="5" t="n">
@@ -9540,7 +9388,7 @@
       </c>
       <c r="M138" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N138" s="3" t="inlineStr">
@@ -9823,34 +9671,34 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
-        <v>9355000</v>
+        <v>8513000</v>
       </c>
       <c r="I143" s="5" t="n">
-        <v>26131</v>
+        <v>23779</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K143" s="5" t="n">
-        <v>8419500</v>
+        <v>8513000</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>23518</v>
+        <v>23779</v>
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N143" s="3" t="inlineStr">
@@ -10203,7 +10051,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
@@ -10211,34 +10059,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H149" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I149" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H149" s="5" t="n">
+        <v>8320000</v>
+      </c>
+      <c r="I149" s="5" t="n">
+        <v>24186</v>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K149" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L149" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>7488000</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>21767</v>
       </c>
       <c r="M149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N149" s="3" t="inlineStr">
@@ -10273,23 +10113,23 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
-        <v>6567000</v>
+        <v>5910300</v>
       </c>
       <c r="I150" s="5" t="n">
-        <v>24875</v>
+        <v>22388</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K150" s="5" t="n">
@@ -10300,7 +10140,7 @@
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N150" s="3" t="inlineStr">
@@ -10583,7 +10423,7 @@
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
@@ -10610,7 +10450,7 @@
       </c>
       <c r="M155" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N155" s="3" t="inlineStr">
@@ -10901,23 +10741,23 @@
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
-        <v>6602000</v>
+        <v>5941800</v>
       </c>
       <c r="I160" s="5" t="n">
-        <v>23748</v>
+        <v>21373</v>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K160" s="5" t="n">
@@ -10928,7 +10768,7 @@
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N160" s="3" t="inlineStr">
@@ -10963,7 +10803,7 @@
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
@@ -10971,34 +10811,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H161" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I161" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H161" s="5" t="n">
+        <v>8295000</v>
+      </c>
+      <c r="I161" s="5" t="n">
+        <v>24113</v>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K161" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L161" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K161" s="5" t="n">
+        <v>7465500</v>
+      </c>
+      <c r="L161" s="5" t="n">
+        <v>21702</v>
       </c>
       <c r="M161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N161" s="3" t="inlineStr">
@@ -11033,34 +10865,34 @@
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
-        <v>6547000</v>
+        <v>5957700</v>
       </c>
       <c r="I162" s="5" t="n">
-        <v>24799</v>
+        <v>22567</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K162" s="5" t="n">
-        <v>5892300</v>
+        <v>5957700</v>
       </c>
       <c r="L162" s="5" t="n">
-        <v>22319</v>
+        <v>22567</v>
       </c>
       <c r="M162" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N162" s="3" t="inlineStr">
@@ -11343,7 +11175,7 @@
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
@@ -11370,7 +11202,7 @@
       </c>
       <c r="M167" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N167" s="3" t="inlineStr">
@@ -11661,23 +11493,23 @@
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
-        <v>6581000</v>
+        <v>5922900</v>
       </c>
       <c r="I172" s="5" t="n">
-        <v>23673</v>
+        <v>21305</v>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K172" s="5" t="n">
@@ -11688,7 +11520,7 @@
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N172" s="3" t="inlineStr">
@@ -11723,7 +11555,7 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
@@ -11731,34 +11563,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H173" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I173" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H173" s="5" t="n">
+        <v>8269000</v>
+      </c>
+      <c r="I173" s="5" t="n">
+        <v>24038</v>
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K173" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L173" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K173" s="5" t="n">
+        <v>7442100</v>
+      </c>
+      <c r="L173" s="5" t="n">
+        <v>21634</v>
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N173" s="3" t="inlineStr">
@@ -11793,34 +11617,34 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
-        <v>6526000</v>
+        <v>5938600</v>
       </c>
       <c r="I174" s="5" t="n">
-        <v>24720</v>
+        <v>22495</v>
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K174" s="5" t="n">
-        <v>5873400</v>
+        <v>5938600</v>
       </c>
       <c r="L174" s="5" t="n">
-        <v>22248</v>
+        <v>22495</v>
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N174" s="3" t="inlineStr">
@@ -12103,7 +11927,7 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
@@ -12130,7 +11954,7 @@
       </c>
       <c r="M179" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N179" s="3" t="inlineStr">
@@ -12421,23 +12245,23 @@
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
-        <v>6561000</v>
+        <v>5904900</v>
       </c>
       <c r="I184" s="5" t="n">
-        <v>23601</v>
+        <v>21241</v>
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K184" s="5" t="n">
@@ -12448,7 +12272,7 @@
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N184" s="3" t="inlineStr">
@@ -12483,7 +12307,7 @@
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
@@ -12491,34 +12315,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H185" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I185" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H185" s="5" t="n">
+        <v>8244000</v>
+      </c>
+      <c r="I185" s="5" t="n">
+        <v>23965</v>
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K185" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L185" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K185" s="5" t="n">
+        <v>7419600</v>
+      </c>
+      <c r="L185" s="5" t="n">
+        <v>21569</v>
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N185" s="3" t="inlineStr">
@@ -12553,34 +12369,34 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
-        <v>6506000</v>
+        <v>5920400</v>
       </c>
       <c r="I186" s="5" t="n">
-        <v>24644</v>
+        <v>22426</v>
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K186" s="5" t="n">
-        <v>5855400</v>
+        <v>5920400</v>
       </c>
       <c r="L186" s="5" t="n">
-        <v>22180</v>
+        <v>22426</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N186" s="3" t="inlineStr">
@@ -13197,23 +13013,23 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
-        <v>6541000</v>
+        <v>5886900</v>
       </c>
       <c r="I196" s="5" t="n">
-        <v>23529</v>
+        <v>21176</v>
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K196" s="5" t="n">
@@ -13224,7 +13040,7 @@
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N196" s="3" t="inlineStr">
@@ -13259,7 +13075,7 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
@@ -13267,34 +13083,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H197" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I197" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H197" s="5" t="n">
+        <v>8219000</v>
+      </c>
+      <c r="I197" s="5" t="n">
+        <v>23892</v>
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K197" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L197" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K197" s="5" t="n">
+        <v>7397100</v>
+      </c>
+      <c r="L197" s="5" t="n">
+        <v>21503</v>
       </c>
       <c r="M197" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N197" s="3" t="inlineStr">
@@ -13329,34 +13137,34 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
-        <v>6486000</v>
+        <v>5967100</v>
       </c>
       <c r="I198" s="5" t="n">
-        <v>24568</v>
+        <v>22603</v>
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K198" s="5" t="n">
-        <v>5837400</v>
+        <v>5967100</v>
       </c>
       <c r="L198" s="5" t="n">
-        <v>22111</v>
+        <v>22603</v>
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N198" s="3" t="inlineStr">
@@ -13418,7 +13226,7 @@
       </c>
       <c r="M199" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N199" s="3" t="inlineStr">
@@ -13453,23 +13261,23 @@
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
-        <v>9584000</v>
+        <v>8625600</v>
       </c>
       <c r="I200" s="5" t="n">
-        <v>24765</v>
+        <v>22288</v>
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K200" s="5" t="n">
@@ -13480,7 +13288,7 @@
       </c>
       <c r="M200" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N200" s="3" t="inlineStr">
@@ -13841,7 +13649,7 @@
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
@@ -13868,7 +13676,7 @@
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N206" s="3" t="inlineStr">
@@ -13965,23 +13773,23 @@
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
-        <v>6520000</v>
+        <v>5868000</v>
       </c>
       <c r="I208" s="5" t="n">
-        <v>23453</v>
+        <v>21108</v>
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K208" s="5" t="n">
@@ -13992,7 +13800,7 @@
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N208" s="3" t="inlineStr">
@@ -14027,7 +13835,7 @@
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -14035,34 +13843,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H209" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I209" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H209" s="5" t="n">
+        <v>8193000</v>
+      </c>
+      <c r="I209" s="5" t="n">
+        <v>23817</v>
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K209" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L209" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K209" s="5" t="n">
+        <v>7373700</v>
+      </c>
+      <c r="L209" s="5" t="n">
+        <v>21435</v>
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N209" s="3" t="inlineStr">
@@ -14097,34 +13897,34 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
-        <v>6466000</v>
+        <v>5884000</v>
       </c>
       <c r="I210" s="5" t="n">
-        <v>24492</v>
+        <v>22288</v>
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K210" s="5" t="n">
-        <v>5819400</v>
+        <v>5884000</v>
       </c>
       <c r="L210" s="5" t="n">
-        <v>22043</v>
+        <v>22288</v>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N210" s="3" t="inlineStr">
@@ -14539,23 +14339,23 @@
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
-        <v>10514000</v>
+        <v>9462600</v>
       </c>
       <c r="I217" s="5" t="n">
-        <v>25153</v>
+        <v>22638</v>
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K217" s="5" t="n">
@@ -14566,7 +14366,7 @@
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N217" s="3" t="inlineStr">
@@ -14601,7 +14401,7 @@
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
@@ -14628,7 +14428,7 @@
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N218" s="3" t="inlineStr">
@@ -14725,23 +14525,23 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
-        <v>6500000</v>
+        <v>5850000</v>
       </c>
       <c r="I220" s="5" t="n">
-        <v>23381</v>
+        <v>21043</v>
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K220" s="5" t="n">
@@ -14752,7 +14552,7 @@
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N220" s="3" t="inlineStr">
@@ -14787,7 +14587,7 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -14795,34 +14595,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H221" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I221" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H221" s="5" t="n">
+        <v>8182000</v>
+      </c>
+      <c r="I221" s="5" t="n">
+        <v>23785</v>
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K221" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L221" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K221" s="5" t="n">
+        <v>7363800</v>
+      </c>
+      <c r="L221" s="5" t="n">
+        <v>21406</v>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N221" s="3" t="inlineStr">
@@ -14857,23 +14649,23 @@
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
-        <v>6445000</v>
+        <v>5800500</v>
       </c>
       <c r="I222" s="5" t="n">
-        <v>24413</v>
+        <v>21972</v>
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K222" s="5" t="n">
@@ -14884,7 +14676,7 @@
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N222" s="3" t="inlineStr">
@@ -15299,23 +15091,23 @@
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
-        <v>10514000</v>
+        <v>9462600</v>
       </c>
       <c r="I229" s="5" t="n">
-        <v>25153</v>
+        <v>22638</v>
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K229" s="5" t="n">
@@ -15326,7 +15118,7 @@
       </c>
       <c r="M229" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N229" s="3" t="inlineStr">
@@ -15485,23 +15277,23 @@
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
-        <v>6500000</v>
+        <v>5850000</v>
       </c>
       <c r="I232" s="5" t="n">
-        <v>23381</v>
+        <v>21043</v>
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K232" s="5" t="n">
@@ -15512,7 +15304,7 @@
       </c>
       <c r="M232" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N232" s="3" t="inlineStr">
@@ -15547,7 +15339,7 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -15555,34 +15347,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H233" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I233" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H233" s="5" t="n">
+        <v>8178000</v>
+      </c>
+      <c r="I233" s="5" t="n">
+        <v>23773</v>
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K233" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L233" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K233" s="5" t="n">
+        <v>7360200</v>
+      </c>
+      <c r="L233" s="5" t="n">
+        <v>21396</v>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N233" s="3" t="inlineStr">
@@ -15617,7 +15401,7 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -15644,7 +15428,7 @@
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N234" s="3" t="inlineStr">
@@ -16245,34 +16029,34 @@
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
-        <v>6481000</v>
+        <v>5962500</v>
       </c>
       <c r="I244" s="5" t="n">
-        <v>23313</v>
+        <v>21448</v>
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K244" s="5" t="n">
-        <v>5832900</v>
+        <v>5962500</v>
       </c>
       <c r="L244" s="5" t="n">
-        <v>20982</v>
+        <v>21448</v>
       </c>
       <c r="M244" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N244" s="3" t="inlineStr">
@@ -16307,7 +16091,7 @@
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
@@ -16315,34 +16099,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H245" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I245" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H245" s="5" t="n">
+        <v>8152000</v>
+      </c>
+      <c r="I245" s="5" t="n">
+        <v>23698</v>
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K245" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L245" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="K245" s="5" t="n">
+        <v>7336800</v>
+      </c>
+      <c r="L245" s="5" t="n">
+        <v>21328</v>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>現金或即時按揭付款計劃</t>
         </is>
       </c>
       <c r="N245" s="3" t="inlineStr">
@@ -16377,34 +16153,34 @@
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
-        <v>6432000</v>
+        <v>5853100</v>
       </c>
       <c r="I246" s="5" t="n">
-        <v>24364</v>
+        <v>22171</v>
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K246" s="5" t="n">
-        <v>5788800</v>
+        <v>5853100</v>
       </c>
       <c r="L246" s="5" t="n">
-        <v>21927</v>
+        <v>22171</v>
       </c>
       <c r="M246" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N246" s="3" t="inlineStr">
@@ -16951,38 +16727,30 @@
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H255" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I255" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H255" s="5" t="n">
+        <v>6052200</v>
+      </c>
+      <c r="I255" s="5" t="n">
+        <v>26200</v>
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K255" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L255" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K255" s="5" t="n">
+        <v>6052200</v>
+      </c>
+      <c r="L255" s="5" t="n">
+        <v>26200</v>
       </c>
       <c r="M255" s="3" t="inlineStr">
         <is>
@@ -16991,7 +16759,7 @@
       </c>
       <c r="N255" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -17021,38 +16789,30 @@
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H256" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I256" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H256" s="5" t="n">
+        <v>6132000</v>
+      </c>
+      <c r="I256" s="5" t="n">
+        <v>25550</v>
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K256" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L256" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K256" s="5" t="n">
+        <v>6132000</v>
+      </c>
+      <c r="L256" s="5" t="n">
+        <v>25550</v>
       </c>
       <c r="M256" s="3" t="inlineStr">
         <is>
@@ -17061,7 +16821,7 @@
       </c>
       <c r="N256" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -17767,17 +17527,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>172</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -17787,7 +17547,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>44</t>
         </is>
       </c>
     </row>
@@ -17880,15 +17640,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
 $1048万
 $29,288/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E5" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
 $872万
@@ -17952,7 +17712,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="M5" s="24" t="inlineStr"/>
+      <c r="M5" s="23" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
@@ -17960,7 +17720,1449 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>A | 418呎 (3房)
+$1249万
+$29,883/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
+$1018万
+$28,433/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 357呎 (2房)
+$847万
+$23,713/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 362呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>F | 387呎 (3房)
+$1136万
+$29,341/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$625万
+$23,684/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="J6" s="24" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$890万
+$25,887/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$624万
+$22,449/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>L | 269呎 (1房)
+$594万
+$22,085/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="M6" s="24" t="inlineStr">
+        <is>
+          <t>M | 386呎 (3房)
+$1031万
+$26,720/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>A | 418呎 (3房)
+$1229万
+$29,397/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
+$1001万
+$27,972/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 357呎 (2房)
+$833万
+$23,324/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>E | 362呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
+        <is>
+          <t>F | 387呎 (3房)
+$1117万
+$28,853/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$618万
+$23,408/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="J7" s="24" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$880万
+$25,593/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K7" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$610万
+$21,950/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="L7" s="22" t="inlineStr">
+        <is>
+          <t>L | 269呎 (1房)
+$600万
+$22,319/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="M7" s="24" t="inlineStr">
+        <is>
+          <t>M | 386呎 (3房)
+$1020万
+$26,420/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>A | 418呎 (3房)
+$1219万
+$29,153/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
+$894万
+$24,969/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 357呎 (2房)
+$826万
+$23,133/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>E | 362呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 387呎 (3房)
+$960万
+$24,805/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$608万
+$23,018/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="J8" s="24" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$875万
+$25,445/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K8" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$607万
+$21,820/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="L8" s="22" t="inlineStr">
+        <is>
+          <t>L | 269呎 (1房)
+$597万
+$22,189/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="M8" s="24" t="inlineStr">
+        <is>
+          <t>M | 386呎 (3房)
+$1014万
+$26,267/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 418呎 (3房)
+$1049万
+$25,101/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
+$985万
+$27,511/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 357呎 (2房)
+$828万
+$23,193/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 362呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 387呎 (3房)
+$952万
+$24,593/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$611万
+$23,136/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="J9" s="24" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$870万
+$25,297/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$616万
+$22,176/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="L9" s="22" t="inlineStr">
+        <is>
+          <t>L | 269呎 (1房)
+$580万
+$21,580/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="M9" s="22" t="inlineStr">
+        <is>
+          <t>M | 386呎 (3房)
+$875万
+$22,677/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 418呎 (3房)
+$1025万
+$24,531/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
+$879万
+$24,554/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 357呎 (2房)
+$812万
+$22,745/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 362呎 (2房)
+$841万
+$23,241/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 387呎 (3房)
+$945万
+$24,417/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$710万
+$22,392/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$600万
+$22,745/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="J10" s="24" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$865万
+$25,148/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K10" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$600万
+$21,568/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="L10" s="22" t="inlineStr">
+        <is>
+          <t>L | 269呎 (1房)
+$583万
+$21,691/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="M10" s="22" t="inlineStr">
+        <is>
+          <t>M | 386呎 (3房)
+$858万
+$22,219/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 418呎 (3房)
+$1003万
+$23,988/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
+$879万
+$24,547/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 357呎 (2房)
+$803万
+$22,487/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 362呎 (2房)
+$832万
+$22,970/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 387呎 (3房)
+$924万
+$23,870/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$714万
+$22,509/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$597万
+$22,612/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="J11" s="24" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$860万
+$25,000/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K11" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$596万
+$21,438/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="L11" s="22" t="inlineStr">
+        <is>
+          <t>L | 269呎 (1房)
+$580万
+$21,562/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="M11" s="22" t="inlineStr">
+        <is>
+          <t>M | 386呎 (3房)
+$843万
+$21,849/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 418呎 (3房)
+$970万
+$23,202/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
+$862万
+$24,071/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 357呎 (2房)
+$796万
+$22,293/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 362呎 (2房)
+$824万
+$22,766/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 387呎 (3房)
+$936万
+$24,186/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$709万
+$22,379/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$607万
+$22,975/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="J12" s="24" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$855万
+$24,852/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$592万
+$21,312/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="L12" s="22" t="inlineStr">
+        <is>
+          <t>L | 269呎 (1房)
+$570万
+$21,202/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="M12" s="22" t="inlineStr">
+        <is>
+          <t>M | 386呎 (3房)
+$827万
+$21,427/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 418呎 (3房)
+$964万
+$23,066/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
+$857万
+$23,933/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 357呎 (2房)
+$791万
+$22,165/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 362呎 (2房)
+$819万
+$22,629/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 387呎 (2房)
+$910万
+$23,519/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$698万
+$22,003/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$590万
+$22,333/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="J13" s="24" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$850万
+$24,703/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K13" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$589万
+$21,186/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="L13" s="22" t="inlineStr">
+        <is>
+          <t>L | 269呎 (1房)
+$567万
+$21,075/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="M13" s="22" t="inlineStr">
+        <is>
+          <t>M | 386呎 (3房)
+$813万
+$21,068/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 418呎 (3房)
+$1030万
+$24,653/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
+$852万
+$23,795/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 357呎 (2房)
+$787万
+$22,036/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 362呎 (2房)
+$834万
+$23,042/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 387呎 (2房)
+$946万
+$24,436/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$718万
+$22,658/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$587万
+$22,227/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="J14" s="24" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$845万
+$24,558/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$612万
+$22,010/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="L14" s="22" t="inlineStr">
+        <is>
+          <t>L | 269呎 (1房)
+$563万
+$20,948/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="M14" s="20" t="inlineStr">
+        <is>
+          <t>M | 386呎 (3房)
+$966万
+$25,016/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 418呎 (3房)
+$1030万
+$24,653/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
+$852万
+$23,795/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 357呎 (2房)
+$787万
+$22,036/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 362呎 (2房)
+$843万
+$23,298/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 387呎 (2房)
+$914万
+$23,605/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$789万
+$24,899/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$587万
+$22,227/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="J15" s="24" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$845万
+$24,558/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K15" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$619万
+$22,252/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="L15" s="22" t="inlineStr">
+        <is>
+          <t>L | 269呎 (1房)
+$563万
+$20,948/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="M15" s="20" t="inlineStr">
+        <is>
+          <t>M | 386呎 (3房)
+$966万
+$25,016/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 418呎 (3房)
+$985万
+$23,572/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
+$851万
+$23,779/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 357呎 (2房)
+$786万
+$22,021/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 362呎 (2房)
+$804万
+$22,222/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 387呎 (2房)
+$894万
+$23,100/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$702万
+$22,142/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$593万
+$22,456/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="J16" s="24" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$835万
+$24,262/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K16" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$578万
+$20,791/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="L16" s="22" t="inlineStr">
+        <is>
+          <t>L | 269呎 (1房)
+$557万
+$20,697/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="M16" s="22" t="inlineStr">
+        <is>
+          <t>M | 386呎 (3房)
+$831万
+$21,523/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 418呎 (3房)
+$976万
+$23,351/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
+$930万
+$25,978/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 357呎 (2房)
+$773万
+$21,650/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 362呎 (2房)
+$799万
+$22,085/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 387呎 (2房)
+$889万
+$22,960/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$683万
+$21,552/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$591万
+$22,388/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="J17" s="24" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$832万
+$24,186/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K17" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$576万
+$20,713/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="L17" s="22" t="inlineStr">
+        <is>
+          <t>L | 269呎 (1房)
+$555万
+$20,633/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="M17" s="22" t="inlineStr">
+        <is>
+          <t>M | 386呎 (3房)
+$816万
+$21,148/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 418呎 (3房)
+$925万
+$22,130/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
+$914万
+$25,517/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 357呎 (2房)
+$759万
+$21,262/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 362呎 (2房)
+$785万
+$21,677/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 387呎 (2房)
+$872万
+$22,542/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$681万
+$21,486/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$596万
+$22,567/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="J18" s="24" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$830万
+$24,113/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K18" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$594万
+$21,373/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="L18" s="22" t="inlineStr">
+        <is>
+          <t>L | 269呎 (1房)
+$553万
+$20,570/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="M18" s="22" t="inlineStr">
+        <is>
+          <t>M | 386呎 (3房)
+$794万
+$20,569/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 418呎 (3房)
+$900万
+$21,527/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 363呎 (2房)
+$795万
+$21,895/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
+$889万
+$24,827/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 357呎 (2房)
+$747万
+$20,912/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 362呎 (2房)
+$771万
+$21,299/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 387呎 (2房)
+$857万
+$22,155/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$687万
+$21,659/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$594万
+$22,495/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="J19" s="24" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$827万
+$24,038/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K19" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$592万
+$21,305/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="L19" s="22" t="inlineStr">
+        <is>
+          <t>L | 269呎 (1房)
+$552万
+$20,506/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="M19" s="22" t="inlineStr">
+        <is>
+          <t>M | 386呎 (3房)
+$792万
+$20,509/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 -
@@ -17968,87 +19170,87 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
+$787万
+$21,687/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
-$1018万
-$28,433/呎
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 357呎 (2房)
+$740万
+$20,718/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 362呎 (2房)
+$783万
+$21,638/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 387呎 (2房)
+$848万
+$21,912/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$677万
+$21,356/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$592万
+$22,426/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="J20" s="24" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$824万
+$23,965/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
-        <is>
-          <t>D | 357呎 (2房)
-$847万
-$23,713/呎
+      <c r="K20" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$590万
+$21,241/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="L20" s="22" t="inlineStr">
+        <is>
+          <t>L | 269呎 (1房)
+$550万
+$20,442/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t>E | 362呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="21" t="inlineStr">
-        <is>
-          <t>F | 387呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I6" s="23" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$625万
-$23,684/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K6" s="23" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$624万
-$22,449/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="L6" s="23" t="inlineStr">
-        <is>
-          <t>L | 269呎 (1房)
-$594万
-$22,085/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="M6" s="21" t="inlineStr">
+      <c r="M20" s="21" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 -
@@ -18057,13 +19259,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 -
@@ -18071,87 +19273,87 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
+$782万
+$21,548/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
-$1001万
-$27,972/呎
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 357呎 (2房)
+$727万
+$20,362/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 362呎 (2房)
+$770万
+$21,264/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 387呎 (2房)
+$863万
+$22,288/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$768万
+$24,237/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$597万
+$22,603/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="J21" s="24" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$822万
+$23,892/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>D | 357呎 (2房)
-$833万
-$23,324/呎
+      <c r="K21" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$589万
+$21,176/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="L21" s="22" t="inlineStr">
+        <is>
+          <t>L | 269呎 (1房)
+$548万
+$20,379/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t>E | 362呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>F | 387呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I7" s="23" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$618万
-$23,408/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K7" s="23" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$610万
-$21,950/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="L7" s="23" t="inlineStr">
-        <is>
-          <t>L | 269呎 (1房)
-$600万
-$22,319/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="M7" s="21" t="inlineStr">
+      <c r="M21" s="21" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 -
@@ -18160,1265 +19362,29 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
+$946万
+$22,638/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
-$993万
-$27,743/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E8" s="23" t="inlineStr">
-        <is>
-          <t>D | 357呎 (2房)
-$826万
-$23,133/呎
+$777万
+$21,409/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t>E | 362呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="23" t="inlineStr">
-        <is>
-          <t>F | 387呎 (3房)
-$960万
-$24,805/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I8" s="23" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$608万
-$23,018/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K8" s="23" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$607万
-$21,820/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="L8" s="23" t="inlineStr">
-        <is>
-          <t>L | 269呎 (1房)
-$597万
-$22,189/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="M8" s="21" t="inlineStr">
-        <is>
-          <t>M | 386呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>A | 418呎 (3房)
-$1049万
-$25,101/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>B | 363呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="22" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
-$985万
-$27,511/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="inlineStr">
-        <is>
-          <t>D | 357呎 (2房)
-$828万
-$23,193/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t>E | 362呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="23" t="inlineStr">
-        <is>
-          <t>F | 387呎 (3房)
-$952万
-$24,593/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I9" s="23" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$611万
-$23,136/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="J9" s="21" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K9" s="23" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$616万
-$22,176/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="L9" s="23" t="inlineStr">
-        <is>
-          <t>L | 269呎 (1房)
-$580万
-$21,580/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="M9" s="23" t="inlineStr">
-        <is>
-          <t>M | 386呎 (3房)
-$875万
-$22,677/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>A | 418呎 (3房)
-$1025万
-$24,531/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>B | 363呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
-$977万
-$27,282/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>D | 357呎 (2房)
-$812万
-$22,745/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>E | 362呎 (2房)
-$841万
-$23,241/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="G10" s="23" t="inlineStr">
-        <is>
-          <t>F | 387呎 (3房)
-$945万
-$24,417/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
-$710万
-$22,392/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="I10" s="23" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$600万
-$22,745/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K10" s="23" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$600万
-$21,568/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="L10" s="23" t="inlineStr">
-        <is>
-          <t>L | 269呎 (1房)
-$583万
-$21,691/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="M10" s="23" t="inlineStr">
-        <is>
-          <t>M | 386呎 (3房)
-$858万
-$22,219/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>A | 418呎 (3房)
-$1003万
-$23,988/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
-        <is>
-          <t>B | 363呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
-$966万
-$26,975/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="inlineStr">
-        <is>
-          <t>D | 357呎 (2房)
-$803万
-$22,487/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t>E | 362呎 (2房)
-$832万
-$22,970/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="G11" s="23" t="inlineStr">
-        <is>
-          <t>F | 387呎 (3房)
-$924万
-$23,870/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="H11" s="23" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
-$714万
-$22,509/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="I11" s="23" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$597万
-$22,612/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="J11" s="21" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K11" s="23" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$596万
-$21,438/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="L11" s="23" t="inlineStr">
-        <is>
-          <t>L | 269呎 (1房)
-$580万
-$21,562/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="M11" s="23" t="inlineStr">
-        <is>
-          <t>M | 386呎 (3房)
-$843万
-$21,849/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>A | 418呎 (3房)
-$970万
-$23,202/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>B | 363呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
-$958万
-$26,746/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="inlineStr">
-        <is>
-          <t>D | 357呎 (2房)
-$796万
-$22,293/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="F12" s="23" t="inlineStr">
-        <is>
-          <t>E | 362呎 (2房)
-$824万
-$22,766/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="G12" s="23" t="inlineStr">
-        <is>
-          <t>F | 387呎 (3房)
-$936万
-$24,186/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="H12" s="23" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
-$709万
-$22,379/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="I12" s="23" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$607万
-$22,975/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="J12" s="21" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K12" s="23" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$592万
-$21,312/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="L12" s="23" t="inlineStr">
-        <is>
-          <t>L | 269呎 (1房)
-$570万
-$21,202/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="M12" s="23" t="inlineStr">
-        <is>
-          <t>M | 386呎 (3房)
-$827万
-$21,427/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>A | 418呎 (3房)
-$964万
-$23,066/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>B | 363呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
-$952万
-$26,592/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>D | 357呎 (2房)
-$791万
-$22,165/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>E | 362呎 (2房)
-$819万
-$22,629/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="G13" s="23" t="inlineStr">
-        <is>
-          <t>F | 387呎 (2房)
-$910万
-$23,519/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="H13" s="23" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
-$698万
-$22,003/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="I13" s="23" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$590万
-$22,333/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K13" s="23" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$589万
-$21,186/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="L13" s="23" t="inlineStr">
-        <is>
-          <t>L | 269呎 (1房)
-$567万
-$21,075/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="M13" s="23" t="inlineStr">
-        <is>
-          <t>M | 386呎 (3房)
-$813万
-$21,068/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B14" s="22" t="inlineStr">
-        <is>
-          <t>A | 418呎 (3房)
-$1145万
-$27,392/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>B | 363呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
-$946万
-$26,439/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>D | 357呎 (2房)
-$787万
-$22,036/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>E | 362呎 (2房)
-$834万
-$23,042/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="G14" s="22" t="inlineStr">
-        <is>
-          <t>F | 387呎 (2房)
-$1039万
-$26,853/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H14" s="23" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
-$718万
-$22,658/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="I14" s="23" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$587万
-$22,227/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K14" s="22" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$672万
-$24,187/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L14" s="23" t="inlineStr">
-        <is>
-          <t>L | 269呎 (1房)
-$563万
-$20,948/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="M14" s="22" t="inlineStr">
-        <is>
-          <t>M | 386呎 (3房)
-$966万
-$25,016/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>A | 418呎 (3房)
-$1145万
-$27,392/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
-        <is>
-          <t>B | 363呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
-$946万
-$26,439/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
-        <is>
-          <t>D | 357呎 (2房)
-$787万
-$22,036/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>E | 362呎 (2房)
-$843万
-$23,298/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="G15" s="23" t="inlineStr">
-        <is>
-          <t>F | 387呎 (2房)
-$914万
-$23,605/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="H15" s="20" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
-$789万
-$24,899/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I15" s="23" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$587万
-$22,227/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="J15" s="21" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K15" s="22" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$672万
-$24,187/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L15" s="23" t="inlineStr">
-        <is>
-          <t>L | 269呎 (1房)
-$563万
-$20,948/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="M15" s="22" t="inlineStr">
-        <is>
-          <t>M | 386呎 (3房)
-$966万
-$25,016/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>A | 418呎 (3房)
-$985万
-$23,572/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>B | 363呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="22" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
-$936万
-$26,131/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="inlineStr">
-        <is>
-          <t>D | 357呎 (2房)
-$786万
-$22,021/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>E | 362呎 (2房)
-$804万
-$22,222/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="G16" s="23" t="inlineStr">
-        <is>
-          <t>F | 387呎 (2房)
-$894万
-$23,100/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="H16" s="23" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
-$702万
-$22,142/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="I16" s="22" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$659万
-$24,951/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J16" s="21" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K16" s="23" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$578万
-$20,791/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="L16" s="23" t="inlineStr">
-        <is>
-          <t>L | 269呎 (1房)
-$557万
-$20,697/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="M16" s="23" t="inlineStr">
-        <is>
-          <t>M | 386呎 (3房)
-$831万
-$21,523/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>A | 418呎 (3房)
-$976万
-$23,351/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>B | 363呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="22" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
-$930万
-$25,978/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E17" s="23" t="inlineStr">
-        <is>
-          <t>D | 357呎 (2房)
-$773万
-$21,650/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="F17" s="23" t="inlineStr">
-        <is>
-          <t>E | 362呎 (2房)
-$799万
-$22,085/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="G17" s="23" t="inlineStr">
-        <is>
-          <t>F | 387呎 (2房)
-$889万
-$22,960/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="H17" s="23" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
-$683万
-$21,552/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="I17" s="22" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$657万
-$24,875/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J17" s="21" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K17" s="23" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$576万
-$20,713/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="L17" s="23" t="inlineStr">
-        <is>
-          <t>L | 269呎 (1房)
-$555万
-$20,633/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="M17" s="23" t="inlineStr">
-        <is>
-          <t>M | 386呎 (3房)
-$816万
-$21,148/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>A | 418呎 (3房)
-$925万
-$22,130/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>B | 363呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="22" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
-$914万
-$25,517/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E18" s="23" t="inlineStr">
-        <is>
-          <t>D | 357呎 (2房)
-$759万
-$21,262/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>E | 362呎 (2房)
-$785万
-$21,677/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="G18" s="23" t="inlineStr">
-        <is>
-          <t>F | 387呎 (2房)
-$872万
-$22,542/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="H18" s="23" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
-$681万
-$21,486/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="I18" s="22" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$655万
-$24,799/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J18" s="21" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K18" s="22" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$660万
-$23,748/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L18" s="23" t="inlineStr">
-        <is>
-          <t>L | 269呎 (1房)
-$553万
-$20,570/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="M18" s="23" t="inlineStr">
-        <is>
-          <t>M | 386呎 (3房)
-$794万
-$20,569/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>A | 418呎 (3房)
-$900万
-$21,527/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="inlineStr">
-        <is>
-          <t>B | 363呎 (2房)
-$795万
-$21,895/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="D19" s="22" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
-$889万
-$24,827/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E19" s="23" t="inlineStr">
-        <is>
-          <t>D | 357呎 (2房)
-$747万
-$20,912/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="F19" s="23" t="inlineStr">
-        <is>
-          <t>E | 362呎 (2房)
-$771万
-$21,299/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="G19" s="23" t="inlineStr">
-        <is>
-          <t>F | 387呎 (2房)
-$857万
-$22,155/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="H19" s="23" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
-$687万
-$21,659/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="I19" s="22" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$653万
-$24,720/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J19" s="21" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K19" s="22" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$658万
-$23,673/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L19" s="23" t="inlineStr">
-        <is>
-          <t>L | 269呎 (1房)
-$552万
-$20,506/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="M19" s="23" t="inlineStr">
-        <is>
-          <t>M | 386呎 (3房)
-$792万
-$20,509/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B20" s="21" t="inlineStr">
-        <is>
-          <t>A | 418呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
-        <is>
-          <t>B | 363呎 (2房)
-$787万
-$21,687/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
 -
@@ -19426,102 +19392,102 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
-$740万
-$20,718/呎
+$722万
+$20,234/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
-$783万
-$21,638/呎
+$745万
+$20,591/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="G20" s="23" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
-$848万
-$21,912/呎
+$838万
+$21,661/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="H20" s="23" t="inlineStr">
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
-$677万
-$21,356/呎
+$673万
+$21,228/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="I20" s="22" t="inlineStr">
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>H | 264呎 (1房)
-$651万
-$24,644/呎
+$588万
+$22,288/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="J22" s="24" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$819万
+$23,817/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J20" s="21" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K20" s="22" t="inlineStr">
+      <c r="K22" s="22" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
-$656万
-$23,601/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L20" s="23" t="inlineStr">
+$587万
+$21,108/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="L22" s="22" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
-$550万
-$20,442/呎
+$546万
+$20,315/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="M20" s="21" t="inlineStr">
+      <c r="M22" s="20" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B21" s="21" t="inlineStr">
+$937万
+$24,272/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="23" t="inlineStr">
+$946万
+$22,638/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
-$782万
-$21,548/呎
+$786万
+$21,647/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
 -
@@ -19529,102 +19495,102 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
-$727万
-$20,362/呎
+$722万
+$20,234/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
-$770万
-$21,264/呎
+$745万
+$20,591/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="G21" s="22" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
-$958万
-$24,765/呎
+$838万
+$21,661/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$671万
+$21,163/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$580万
+$21,972/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="J23" s="24" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$818万
+$23,785/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H21" s="20" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
-$768万
-$24,237/呎
+      <c r="K23" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$585万
+$21,043/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="L23" s="22" t="inlineStr">
+        <is>
+          <t>L | 269呎 (1房)
+$557万
+$20,701/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="M23" s="20" t="inlineStr">
+        <is>
+          <t>M | 386呎 (3房)
+$934万
+$24,199/呎
 (在售)</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$649万
-$24,568/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J21" s="21" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K21" s="22" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$654万
-$23,529/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L21" s="23" t="inlineStr">
-        <is>
-          <t>L | 269呎 (1房)
-$548万
-$20,379/呎
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 418呎 (3房)
+$869万
+$20,790/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="M21" s="21" t="inlineStr">
-        <is>
-          <t>M | 386呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B22" s="22" t="inlineStr">
-        <is>
-          <t>A | 418呎 (3房)
-$1051万
-$25,153/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
-$777万
-$21,409/呎
+$767万
+$21,131/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
 -
@@ -19632,102 +19598,102 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
-$722万
-$20,234/呎
+$713万
+$19,974/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="F22" s="23" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
-$745万
-$20,591/呎
+$736万
+$20,320/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="G22" s="23" t="inlineStr">
+      <c r="G24" s="22" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
-$838万
-$21,661/呎
+$818万
+$21,144/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="H22" s="23" t="inlineStr">
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
-$673万
-$21,228/呎
+$671万
+$21,163/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="I22" s="22" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>H | 264呎 (1房)
-$647万
-$24,492/呎
+$644万
+$24,413/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J24" s="24" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$818万
+$23,773/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J22" s="21" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K22" s="22" t="inlineStr">
+      <c r="K24" s="22" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
-$652万
-$23,453/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L22" s="23" t="inlineStr">
+$585万
+$21,043/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="L24" s="22" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
-$546万
-$20,315/呎
+$545万
+$20,252/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="M22" s="22" t="inlineStr">
+      <c r="M24" s="22" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
-$937万
-$24,272/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B23" s="22" t="inlineStr">
+$782万
+$20,259/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
-$1051万
-$25,153/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C23" s="23" t="inlineStr">
+$867万
+$20,749/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
-$786万
-$21,647/呎
+$758万
+$20,888/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
 -
@@ -19735,213 +19701,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
-        <is>
-          <t>D | 357呎 (2房)
-$722万
-$20,234/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="F23" s="23" t="inlineStr">
-        <is>
-          <t>E | 362呎 (2房)
-$745万
-$20,591/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="G23" s="23" t="inlineStr">
-        <is>
-          <t>F | 387呎 (2房)
-$838万
-$21,661/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="H23" s="23" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
-$671万
-$21,163/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="I23" s="22" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$644万
-$24,413/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J23" s="21" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K23" s="22" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$650万
-$23,381/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L23" s="23" t="inlineStr">
-        <is>
-          <t>L | 269呎 (1房)
-$557万
-$20,701/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="M23" s="22" t="inlineStr">
-        <is>
-          <t>M | 386呎 (3房)
-$934万
-$24,199/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B24" s="23" t="inlineStr">
-        <is>
-          <t>A | 418呎 (3房)
-$869万
-$20,790/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="C24" s="23" t="inlineStr">
-        <is>
-          <t>B | 363呎 (2房)
-$767万
-$21,131/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="23" t="inlineStr">
-        <is>
-          <t>D | 357呎 (2房)
-$713万
-$19,974/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="F24" s="23" t="inlineStr">
-        <is>
-          <t>E | 362呎 (2房)
-$736万
-$20,320/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="G24" s="23" t="inlineStr">
-        <is>
-          <t>F | 387呎 (2房)
-$818万
-$21,144/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="H24" s="23" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
-$671万
-$21,163/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="I24" s="22" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$644万
-$24,413/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J24" s="21" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K24" s="22" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$650万
-$23,381/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L24" s="23" t="inlineStr">
-        <is>
-          <t>L | 269呎 (1房)
-$545万
-$20,252/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="M24" s="23" t="inlineStr">
-        <is>
-          <t>M | 386呎 (3房)
-$782万
-$20,259/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B25" s="23" t="inlineStr">
-        <is>
-          <t>A | 418呎 (3房)
-$867万
-$20,749/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="C25" s="23" t="inlineStr">
-        <is>
-          <t>B | 363呎 (2房)
-$758万
-$20,888/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
 $704万
@@ -19949,7 +19709,7 @@
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="F25" s="23" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
 $723万
@@ -19957,7 +19717,7 @@
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="G25" s="23" t="inlineStr">
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
 $807万
@@ -19965,7 +19725,7 @@
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="H25" s="23" t="inlineStr">
+      <c r="H25" s="22" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
 $675万
@@ -19976,28 +19736,28 @@
       <c r="I25" s="22" t="inlineStr">
         <is>
           <t>H | 264呎 (1房)
-$643万
-$24,364/呎
+$585万
+$22,171/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="J25" s="24" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$815万
+$23,698/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J25" s="21" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="K25" s="22" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
-$648万
-$23,313/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L25" s="23" t="inlineStr">
+$596万
+$21,448/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="L25" s="22" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
 $549万
@@ -20005,7 +19765,7 @@
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="M25" s="23" t="inlineStr">
+      <c r="M25" s="22" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 $788万
@@ -20020,7 +19780,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>A | 380呎 (3房)
 $961万
@@ -20092,20 +19852,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K26" s="20" t="inlineStr">
+      <c r="K26" s="22" t="inlineStr">
         <is>
           <t>K | 240呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="L26" s="20" t="inlineStr">
+$613万
+$25,550/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="L26" s="22" t="inlineStr">
         <is>
           <t>L | 231呎 (1房)
-招标单位
--
-(在售)</t>
+$605万
+$26,200/呎
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="M26" s="20" t="inlineStr">

--- a/files/九龙-红磡-映汇.xlsx
+++ b/files/九龙-红磡-映汇.xlsx
@@ -11927,23 +11927,23 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
-        <v>8888000</v>
+        <v>7999200</v>
       </c>
       <c r="I179" s="5" t="n">
-        <v>24827</v>
+        <v>22344</v>
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K179" s="5" t="n">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="M179" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N179" s="3" t="inlineStr">
@@ -13199,34 +13199,34 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
-        <v>7683000</v>
+        <v>6991500</v>
       </c>
       <c r="I199" s="5" t="n">
-        <v>24237</v>
+        <v>22055</v>
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K199" s="5" t="n">
-        <v>6914700</v>
+        <v>6991500</v>
       </c>
       <c r="L199" s="5" t="n">
-        <v>21813</v>
+        <v>22055</v>
       </c>
       <c r="M199" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N199" s="3" t="inlineStr">
@@ -17527,7 +17527,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>174</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -19075,12 +19075,12 @@
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
-$889万
-$24,827/呎
-(在售)</t>
+$800万
+$22,344/呎
+(26年-09月-17日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -19313,12 +19313,12 @@
 (26年-09月-16日)</t>
         </is>
       </c>
-      <c r="H21" s="20" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
-$768万
-$24,237/呎
-(在售)</t>
+$699万
+$22,055/呎
+(26年-09月-20日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">

--- a/files/九龙-红磡-映汇.xlsx
+++ b/files/九龙-红磡-映汇.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -130,11 +130,6 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -212,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -281,9 +276,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -666,7 +658,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -1354,7 +1346,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1529,7 +1521,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1556,7 +1548,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1715,7 +1707,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1742,7 +1734,7 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -1909,7 +1901,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1936,7 +1928,7 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -2130,7 +2122,7 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -2235,7 +2227,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -2262,7 +2254,7 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -2297,7 +2289,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -2324,7 +2316,7 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -2483,7 +2475,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2510,7 +2502,7 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -2677,7 +2669,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -2704,7 +2696,7 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -2871,23 +2863,23 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
-        <v>10014000</v>
+        <v>9012600</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>27972</v>
+        <v>25175</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="5" t="n">
@@ -2898,7 +2890,7 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -3003,7 +2995,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -3030,7 +3022,7 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -3065,7 +3057,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -3092,7 +3084,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -3251,7 +3243,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -3278,7 +3270,7 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
@@ -3771,7 +3763,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -3798,7 +3790,7 @@
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
@@ -3966,10 +3958,10 @@
         </is>
       </c>
       <c r="H52" s="5" t="n">
-        <v>6164900</v>
+        <v>6030900</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>22176</v>
+        <v>21694</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -3977,10 +3969,10 @@
         </is>
       </c>
       <c r="K52" s="5" t="n">
-        <v>6164900</v>
+        <v>6030900</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>22176</v>
+        <v>21694</v>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
@@ -4019,7 +4011,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -4046,7 +4038,7 @@
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -4434,7 +4426,7 @@
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
@@ -4787,7 +4779,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -4814,7 +4806,7 @@
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
@@ -5539,7 +5531,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -5566,7 +5558,7 @@
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
@@ -6291,7 +6283,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
@@ -6318,7 +6310,7 @@
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N89" s="3" t="inlineStr">
@@ -7043,7 +7035,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -7070,7 +7062,7 @@
       </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N101" s="3" t="inlineStr">
@@ -7636,7 +7628,7 @@
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N110" s="3" t="inlineStr">
@@ -7795,7 +7787,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -7822,7 +7814,7 @@
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N113" s="3" t="inlineStr">
@@ -7990,10 +7982,10 @@
         </is>
       </c>
       <c r="H116" s="5" t="n">
-        <v>9456700</v>
+        <v>9352800</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>24436</v>
+        <v>24167</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
@@ -8001,10 +7993,10 @@
         </is>
       </c>
       <c r="K116" s="5" t="n">
-        <v>9456700</v>
+        <v>9352800</v>
       </c>
       <c r="L116" s="5" t="n">
-        <v>24436</v>
+        <v>24167</v>
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
@@ -8388,7 +8380,7 @@
       </c>
       <c r="M122" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N122" s="3" t="inlineStr">
@@ -8547,7 +8539,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
@@ -8574,7 +8566,7 @@
       </c>
       <c r="M125" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N125" s="3" t="inlineStr">
@@ -8698,7 +8690,7 @@
       </c>
       <c r="M127" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N127" s="3" t="inlineStr">
@@ -9299,7 +9291,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
@@ -9326,7 +9318,7 @@
       </c>
       <c r="M137" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N137" s="3" t="inlineStr">
@@ -9870,7 +9862,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -10051,7 +10043,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
@@ -10078,7 +10070,7 @@
       </c>
       <c r="M149" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N149" s="3" t="inlineStr">
@@ -10450,7 +10442,7 @@
       </c>
       <c r="M155" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N155" s="3" t="inlineStr">
@@ -10803,7 +10795,7 @@
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
@@ -10830,7 +10822,7 @@
       </c>
       <c r="M161" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N161" s="3" t="inlineStr">
@@ -11202,7 +11194,7 @@
       </c>
       <c r="M167" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N167" s="3" t="inlineStr">
@@ -11555,7 +11547,7 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
@@ -11582,7 +11574,7 @@
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N173" s="3" t="inlineStr">
@@ -12307,7 +12299,7 @@
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
@@ -12334,7 +12326,7 @@
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N185" s="3" t="inlineStr">
@@ -13075,7 +13067,7 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
@@ -13102,7 +13094,7 @@
       </c>
       <c r="M197" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N197" s="3" t="inlineStr">
@@ -13676,7 +13668,7 @@
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N206" s="3" t="inlineStr">
@@ -13835,7 +13827,7 @@
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -13862,7 +13854,7 @@
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N209" s="3" t="inlineStr">
@@ -14428,7 +14420,7 @@
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N218" s="3" t="inlineStr">
@@ -14587,7 +14579,7 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -14614,7 +14606,7 @@
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N221" s="3" t="inlineStr">
@@ -15339,7 +15331,7 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -15366,7 +15358,7 @@
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N233" s="3" t="inlineStr">
@@ -15401,23 +15393,23 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
-        <v>6445000</v>
+        <v>5800500</v>
       </c>
       <c r="I234" s="5" t="n">
-        <v>24413</v>
+        <v>21972</v>
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K234" s="5" t="n">
@@ -15428,7 +15420,7 @@
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N234" s="3" t="inlineStr">
@@ -15786,7 +15778,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15972,7 +15964,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -16091,7 +16083,7 @@
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
@@ -16118,7 +16110,7 @@
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N245" s="3" t="inlineStr">
@@ -17527,17 +17519,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>176</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -17720,12 +17712,12 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 $1249万
 $29,883/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -17760,12 +17752,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 387呎 (3房)
 $1136万
 $29,341/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -17784,12 +17776,12 @@
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="J6" s="24" t="inlineStr">
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 $890万
 $25,887/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K6" s="22" t="inlineStr">
@@ -17808,12 +17800,12 @@
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="M6" s="24" t="inlineStr">
+      <c r="M6" s="20" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 $1031万
 $26,720/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -17823,12 +17815,12 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 $1229万
 $29,397/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -17839,12 +17831,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
-$1001万
-$27,972/呎
-(在售)</t>
+$901万
+$25,175/呎
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -17863,12 +17855,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 387呎 (3房)
 $1117万
 $28,853/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -17887,12 +17879,12 @@
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="J7" s="24" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 $880万
 $25,593/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K7" s="22" t="inlineStr">
@@ -17911,12 +17903,12 @@
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="M7" s="24" t="inlineStr">
+      <c r="M7" s="20" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 $1020万
 $26,420/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -17926,12 +17918,12 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 $1219万
 $29,153/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -17990,12 +17982,12 @@
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="J8" s="24" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 $875万
 $25,445/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K8" s="22" t="inlineStr">
@@ -18014,12 +18006,12 @@
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="M8" s="24" t="inlineStr">
+      <c r="M8" s="20" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 $1014万
 $26,267/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -18093,19 +18085,19 @@
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="J9" s="24" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 $870万
 $25,297/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K9" s="22" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
-$616万
-$22,176/呎
+$603万
+$21,694/呎
 (26年-09月-12日)</t>
         </is>
       </c>
@@ -18196,12 +18188,12 @@
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="J10" s="24" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 $865万
 $25,148/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K10" s="22" t="inlineStr">
@@ -18299,12 +18291,12 @@
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="J11" s="24" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 $860万
 $25,000/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K11" s="22" t="inlineStr">
@@ -18402,12 +18394,12 @@
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="J12" s="24" t="inlineStr">
+      <c r="J12" s="20" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 $855万
 $24,852/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K12" s="22" t="inlineStr">
@@ -18505,12 +18497,12 @@
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="J13" s="24" t="inlineStr">
+      <c r="J13" s="20" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 $850万
 $24,703/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K13" s="22" t="inlineStr">
@@ -18587,8 +18579,8 @@
       <c r="G14" s="22" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
-$946万
-$24,436/呎
+$935万
+$24,167/呎
 (26年-09月-16日)</t>
         </is>
       </c>
@@ -18608,12 +18600,12 @@
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="J14" s="24" t="inlineStr">
+      <c r="J14" s="20" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 $845万
 $24,558/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K14" s="22" t="inlineStr">
@@ -18711,12 +18703,12 @@
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="J15" s="24" t="inlineStr">
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 $845万
 $24,558/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K15" s="22" t="inlineStr">
@@ -18814,12 +18806,12 @@
 (26年-09月-16日)</t>
         </is>
       </c>
-      <c r="J16" s="24" t="inlineStr">
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 $835万
 $24,262/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
@@ -18917,12 +18909,12 @@
 (26年-09月-16日)</t>
         </is>
       </c>
-      <c r="J17" s="24" t="inlineStr">
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 $832万
 $24,186/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K17" s="22" t="inlineStr">
@@ -18946,7 +18938,7 @@
           <t>M | 386呎 (3房)
 $816万
 $21,148/呎
-(26年-09月-12日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
     </row>
@@ -19020,12 +19012,12 @@
 (26年-09月-16日)</t>
         </is>
       </c>
-      <c r="J18" s="24" t="inlineStr">
+      <c r="J18" s="20" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 $830万
 $24,113/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K18" s="22" t="inlineStr">
@@ -19123,12 +19115,12 @@
 (26年-09月-16日)</t>
         </is>
       </c>
-      <c r="J19" s="24" t="inlineStr">
+      <c r="J19" s="20" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 $827万
 $24,038/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K19" s="22" t="inlineStr">
@@ -19226,12 +19218,12 @@
 (26年-09月-16日)</t>
         </is>
       </c>
-      <c r="J20" s="24" t="inlineStr">
+      <c r="J20" s="20" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 $824万
 $23,965/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
@@ -19329,12 +19321,12 @@
 (26年-09月-16日)</t>
         </is>
       </c>
-      <c r="J21" s="24" t="inlineStr">
+      <c r="J21" s="20" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 $822万
 $23,892/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K21" s="22" t="inlineStr">
@@ -19432,12 +19424,12 @@
 (26年-09月-16日)</t>
         </is>
       </c>
-      <c r="J22" s="24" t="inlineStr">
+      <c r="J22" s="20" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 $819万
 $23,817/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -19535,12 +19527,12 @@
 (26年-09月-16日)</t>
         </is>
       </c>
-      <c r="J23" s="24" t="inlineStr">
+      <c r="J23" s="20" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 $818万
 $23,785/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -19587,7 +19579,7 @@
           <t>B | 363呎 (2房)
 $767万
 $21,131/呎
-(26年-09月-12日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -19630,20 +19622,20 @@
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="I24" s="20" t="inlineStr">
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>H | 264呎 (1房)
-$644万
-$24,413/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J24" s="24" t="inlineStr">
+$580万
+$21,972/呎
+(26年-09月-22日)</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 $818万
 $23,773/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
@@ -19741,12 +19733,12 @@
 (26年-09月-16日)</t>
         </is>
       </c>
-      <c r="J25" s="24" t="inlineStr">
+      <c r="J25" s="20" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 $815万
 $23,698/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -19762,7 +19754,7 @@
           <t>L | 269呎 (1房)
 $549万
 $20,406/呎
-(26年-09月-12日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="M25" s="22" t="inlineStr">

--- a/files/九龙-红磡-映汇.xlsx
+++ b/files/九龙-红磡-映汇.xlsx
@@ -1262,7 +1262,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="H58" s="5" t="n">
-        <v>8280000</v>
+        <v>8189100</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>23193</v>
+        <v>22939</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="K58" s="5" t="n">
-        <v>8280000</v>
+        <v>8189100</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>23193</v>
+        <v>22939</v>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
@@ -4399,23 +4399,23 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
-        <v>9849000</v>
+        <v>8864100</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>27511</v>
+        <v>24760</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="5" t="n">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -6354,10 +6354,10 @@
         </is>
       </c>
       <c r="H90" s="5" t="n">
-        <v>6065500</v>
+        <v>5999600</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>22975</v>
+        <v>22726</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
@@ -6365,10 +6365,10 @@
         </is>
       </c>
       <c r="K90" s="5" t="n">
-        <v>6065500</v>
+        <v>5999600</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>22975</v>
+        <v>22726</v>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
@@ -7601,23 +7601,23 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
-        <v>9656000</v>
+        <v>8690400</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>25016</v>
+        <v>22514</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K110" s="5" t="n">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N110" s="3" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -15902,7 +15902,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15964,14 +15964,14 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
-        <v>5489100</v>
+        <v>5428800</v>
       </c>
       <c r="I243" s="5" t="n">
-        <v>20406</v>
+        <v>20181</v>
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
@@ -15979,10 +15979,10 @@
         </is>
       </c>
       <c r="K243" s="5" t="n">
-        <v>5489100</v>
+        <v>5428800</v>
       </c>
       <c r="L243" s="5" t="n">
-        <v>20406</v>
+        <v>20181</v>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
@@ -17408,7 +17408,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17519,7 +17519,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -17529,7 +17529,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>178</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -17645,7 +17645,7 @@
           <t>D | 357呎 (2房)
 $872万
 $24,424/呎
-(26年-09月-12日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -17797,7 +17797,7 @@
           <t>L | 269呎 (1房)
 $594万
 $22,085/呎
-(26年-09月-12日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="M6" s="20" t="inlineStr">
@@ -17892,7 +17892,7 @@
           <t>K | 278呎 (1房)
 $610万
 $21,950/呎
-(26年-09月-12日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="L7" s="22" t="inlineStr">
@@ -17900,7 +17900,7 @@
           <t>L | 269呎 (1房)
 $600万
 $22,319/呎
-(26年-09月-12日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="M7" s="20" t="inlineStr">
@@ -18003,7 +18003,7 @@
           <t>L | 269呎 (1房)
 $597万
 $22,189/呎
-(26年-09月-12日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="M8" s="20" t="inlineStr">
@@ -18037,19 +18037,19 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
-$985万
-$27,511/呎
-(在售)</t>
+$886万
+$24,760/呎
+(26年-09月-27日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
-$828万
-$23,193/呎
+$819万
+$22,939/呎
 (26年-09月-12日)</t>
         </is>
       </c>
@@ -18098,7 +18098,7 @@
           <t>K | 278呎 (1房)
 $603万
 $21,694/呎
-(26年-09月-12日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="L9" s="22" t="inlineStr">
@@ -18312,7 +18312,7 @@
           <t>L | 269呎 (1房)
 $580万
 $21,562/呎
-(26年-09月-12日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="M11" s="22" t="inlineStr">
@@ -18320,7 +18320,7 @@
           <t>M | 386呎 (3房)
 $843万
 $21,849/呎
-(26年-09月-12日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
     </row>
@@ -18389,8 +18389,8 @@
       <c r="I12" s="22" t="inlineStr">
         <is>
           <t>H | 264呎 (1房)
-$607万
-$22,975/呎
+$600万
+$22,726/呎
 (26年-09月-12日)</t>
         </is>
       </c>
@@ -18621,10 +18621,113 @@
           <t>L | 269呎 (1房)
 $563万
 $20,948/呎
+(26年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="M14" s="22" t="inlineStr">
+        <is>
+          <t>M | 386呎 (3房)
+$869万
+$22,514/呎
+(26年-09月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 418呎 (3房)
+$1030万
+$24,653/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
+$852万
+$23,795/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 357呎 (2房)
+$787万
+$22,036/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="M14" s="20" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 362呎 (2房)
+$843万
+$23,298/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 387呎 (2房)
+$914万
+$23,605/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$789万
+$24,899/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$587万
+$22,227/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$845万
+$24,558/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K15" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$619万
+$22,252/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="L15" s="22" t="inlineStr">
+        <is>
+          <t>L | 269呎 (1房)
+$563万
+$20,948/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="M15" s="20" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
 $966万
@@ -18633,21 +18736,21 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
-$1030万
-$24,653/呎
-(26年-09月-16日)</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
+$985万
+$23,572/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
 -
@@ -18655,102 +18758,102 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
-$852万
-$23,795/呎
+$851万
+$23,779/呎
 (26年-09月-16日)</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
-$787万
-$22,036/呎
+$786万
+$22,021/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
-$843万
-$23,298/呎
+$804万
+$22,222/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
-$914万
-$23,605/呎
+$894万
+$23,100/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="H15" s="20" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
-$789万
-$24,899/呎
+$702万
+$22,142/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$593万
+$22,456/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$835万
+$24,262/呎
 (在售)</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$587万
-$22,227/呎
+      <c r="K16" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$578万
+$20,791/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="J15" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
-$845万
-$24,558/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K15" s="22" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$619万
-$22,252/呎
-(26年-09月-16日)</t>
-        </is>
-      </c>
-      <c r="L15" s="22" t="inlineStr">
+      <c r="L16" s="22" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
-$563万
-$20,948/呎
+$557万
+$20,697/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="M15" s="20" t="inlineStr">
+      <c r="M16" s="22" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
-$966万
-$25,016/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="inlineStr">
+$831万
+$21,523/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
-$985万
-$23,572/呎
+$976万
+$23,351/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
 -
@@ -18758,102 +18861,102 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
-$851万
-$23,779/呎
+$930万
+$25,978/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 357呎 (2房)
+$773万
+$21,650/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 362呎 (2房)
+$799万
+$22,085/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 387呎 (2房)
+$889万
+$22,960/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$683万
+$21,552/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$591万
+$22,388/呎
 (26年-09月-16日)</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
-        <is>
-          <t>D | 357呎 (2房)
-$786万
-$22,021/呎
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$832万
+$24,186/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K17" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$576万
+$20,713/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
-        <is>
-          <t>E | 362呎 (2房)
-$804万
-$22,222/呎
+      <c r="L17" s="22" t="inlineStr">
+        <is>
+          <t>L | 269呎 (1房)
+$555万
+$20,633/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
-        <is>
-          <t>F | 387呎 (2房)
-$894万
-$23,100/呎
+      <c r="M17" s="22" t="inlineStr">
+        <is>
+          <t>M | 386呎 (3房)
+$816万
+$21,148/呎
+(26年-09月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 418呎 (3房)
+$925万
+$22,130/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
-$702万
-$22,142/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="I16" s="22" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$593万
-$22,456/呎
-(26年-09月-16日)</t>
-        </is>
-      </c>
-      <c r="J16" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
-$835万
-$24,262/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K16" s="22" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$578万
-$20,791/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="L16" s="22" t="inlineStr">
-        <is>
-          <t>L | 269呎 (1房)
-$557万
-$20,697/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="M16" s="22" t="inlineStr">
-        <is>
-          <t>M | 386呎 (3房)
-$831万
-$21,523/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>A | 418呎 (3房)
-$976万
-$23,351/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
 -
@@ -18861,109 +18964,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
-$930万
-$25,978/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E17" s="22" t="inlineStr">
-        <is>
-          <t>D | 357呎 (2房)
-$773万
-$21,650/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr">
-        <is>
-          <t>E | 362呎 (2房)
-$799万
-$22,085/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="G17" s="22" t="inlineStr">
-        <is>
-          <t>F | 387呎 (2房)
-$889万
-$22,960/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="H17" s="22" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
-$683万
-$21,552/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="I17" s="22" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$591万
-$22,388/呎
-(26年-09月-16日)</t>
-        </is>
-      </c>
-      <c r="J17" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
-$832万
-$24,186/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K17" s="22" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$576万
-$20,713/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="L17" s="22" t="inlineStr">
-        <is>
-          <t>L | 269呎 (1房)
-$555万
-$20,633/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="M17" s="22" t="inlineStr">
-        <is>
-          <t>M | 386呎 (3房)
-$816万
-$21,148/呎
-(26年-09月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>A | 418呎 (3房)
-$925万
-$22,130/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>B | 363呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
@@ -19373,7 +19373,7 @@
           <t>B | 363呎 (2房)
 $777万
 $21,409/呎
-(26年-09月-12日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -19476,7 +19476,7 @@
           <t>B | 363呎 (2房)
 $786万
 $21,647/呎
-(26年-09月-12日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -19659,7 +19659,7 @@
           <t>M | 386呎 (3房)
 $782万
 $20,259/呎
-(26年-09月-12日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
     </row>
@@ -19752,9 +19752,9 @@
       <c r="L25" s="22" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
-$549万
-$20,406/呎
-(26年-09月-24日)</t>
+$543万
+$20,181/呎
+(26年-09月-12日)</t>
         </is>
       </c>
       <c r="M25" s="22" t="inlineStr">
@@ -19762,7 +19762,7 @@
           <t>M | 386呎 (3房)
 $788万
 $20,421/呎
-(26年-09月-12日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
     </row>
@@ -19777,7 +19777,7 @@
           <t>A | 380呎 (3房)
 $961万
 $25,300/呎
-(26年-09月-12日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">

--- a/files/九龙-红磡-映汇.xlsx
+++ b/files/九龙-红磡-映汇.xlsx
@@ -2038,7 +2038,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6916,14 +6916,14 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
-        <v>5669100</v>
+        <v>5834900</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>21075</v>
+        <v>21691</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
@@ -6931,10 +6931,10 @@
         </is>
       </c>
       <c r="K99" s="5" t="n">
-        <v>5669100</v>
+        <v>5834900</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>21075</v>
+        <v>21691</v>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10924,7 +10924,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -11048,7 +11048,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -11167,23 +11167,23 @@
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
-        <v>9135000</v>
+        <v>8221500</v>
       </c>
       <c r="I167" s="5" t="n">
-        <v>25517</v>
+        <v>22965</v>
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K167" s="5" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="M167" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N167" s="3" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12490,7 +12490,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12746,7 +12746,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12948,7 +12948,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13514,7 +13514,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -14142,7 +14142,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -14336,7 +14336,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14460,7 +14460,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14708,7 +14708,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14832,7 +14832,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16336,7 +16336,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16398,7 +16398,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16530,7 +16530,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16592,7 +16592,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -17519,7 +17519,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -17529,7 +17529,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>179</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -17741,7 +17741,7 @@
           <t>D | 357呎 (2房)
 $847万
 $23,713/呎
-(26年-09月-12日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -17876,7 +17876,7 @@
           <t>H | 264呎 (1房)
 $618万
 $23,408/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -17947,7 +17947,7 @@
           <t>D | 357呎 (2房)
 $826万
 $23,133/呎
-(26年-09月-12日)</t>
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -17963,7 +17963,7 @@
           <t>F | 387呎 (3房)
 $960万
 $24,805/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -18066,7 +18066,7 @@
           <t>F | 387呎 (3房)
 $952万
 $24,593/呎
-(26年-09月-12日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -18082,7 +18082,7 @@
           <t>H | 264呎 (1房)
 $611万
 $23,136/呎
-(26年-09月-12日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -18106,7 +18106,7 @@
           <t>L | 269呎 (1房)
 $580万
 $21,580/呎
-(26年-09月-12日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="M9" s="22" t="inlineStr">
@@ -18129,7 +18129,7 @@
           <t>A | 418呎 (3房)
 $1025万
 $24,531/呎
-(26年-09月-12日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -18145,7 +18145,7 @@
           <t>C | 358呎 (2房)
 $879万
 $24,554/呎
-(26年-09月-16日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -18161,7 +18161,7 @@
           <t>E | 362呎 (2房)
 $841万
 $23,241/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -18169,7 +18169,7 @@
           <t>F | 387呎 (3房)
 $945万
 $24,417/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
@@ -18185,7 +18185,7 @@
           <t>H | 264呎 (1房)
 $600万
 $22,745/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -18201,7 +18201,7 @@
           <t>K | 278呎 (1房)
 $600万
 $21,568/呎
-(26年-09月-12日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="L10" s="22" t="inlineStr">
@@ -18217,7 +18217,7 @@
           <t>M | 386呎 (3房)
 $858万
 $22,219/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
     </row>
@@ -18232,7 +18232,7 @@
           <t>A | 418呎 (3房)
 $1003万
 $23,988/呎
-(26年-09月-12日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -18256,7 +18256,7 @@
           <t>D | 357呎 (2房)
 $803万
 $22,487/呎
-(26年-09月-12日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -18264,7 +18264,7 @@
           <t>E | 362呎 (2房)
 $832万
 $22,970/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -18272,7 +18272,7 @@
           <t>F | 387呎 (3房)
 $924万
 $23,870/呎
-(26年-09月-12日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -18280,7 +18280,7 @@
           <t>G | 317呎 (1房)
 $714万
 $22,509/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -18288,7 +18288,7 @@
           <t>H | 264呎 (1房)
 $597万
 $22,612/呎
-(26年-09月-12日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -18304,7 +18304,7 @@
           <t>K | 278呎 (1房)
 $596万
 $21,438/呎
-(26年-09月-12日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="L11" s="22" t="inlineStr">
@@ -18335,7 +18335,7 @@
           <t>A | 418呎 (3房)
 $970万
 $23,202/呎
-(26年-09月-12日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -18351,7 +18351,7 @@
           <t>C | 358呎 (2房)
 $862万
 $24,071/呎
-(26年-09月-16日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -18367,7 +18367,7 @@
           <t>E | 362呎 (2房)
 $824万
 $22,766/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -18375,7 +18375,7 @@
           <t>F | 387呎 (3房)
 $936万
 $24,186/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -18383,7 +18383,7 @@
           <t>G | 317呎 (1房)
 $709万
 $22,379/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -18415,7 +18415,7 @@
           <t>L | 269呎 (1房)
 $570万
 $21,202/呎
-(26年-09月-12日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="M12" s="22" t="inlineStr">
@@ -18438,7 +18438,7 @@
           <t>A | 418呎 (3房)
 $964万
 $23,066/呎
-(26年-09月-12日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -18454,7 +18454,7 @@
           <t>C | 358呎 (2房)
 $857万
 $23,933/呎
-(26年-09月-16日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -18470,7 +18470,7 @@
           <t>E | 362呎 (2房)
 $819万
 $22,629/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -18478,7 +18478,7 @@
           <t>F | 387呎 (2房)
 $910万
 $23,519/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -18486,7 +18486,7 @@
           <t>G | 317呎 (1房)
 $698万
 $22,003/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -18494,7 +18494,7 @@
           <t>H | 264呎 (1房)
 $590万
 $22,333/呎
-(26年-09月-12日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -18516,9 +18516,9 @@
       <c r="L13" s="22" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
-$567万
-$21,075/呎
-(26年-09月-12日)</t>
+$583万
+$21,691/呎
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="M13" s="22" t="inlineStr">
@@ -18526,7 +18526,7 @@
           <t>M | 386呎 (3房)
 $813万
 $21,068/呎
-(26年-09月-12日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -18537,6 +18537,109 @@
         </is>
       </c>
       <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 418呎 (3房)
+$1030万
+$24,653/呎
+(26年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
+$852万
+$23,795/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 357呎 (2房)
+$787万
+$22,036/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 362呎 (2房)
+$834万
+$23,042/呎
+(26年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 387呎 (2房)
+$935万
+$24,167/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$718万
+$22,658/呎
+(26年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$587万
+$22,227/呎
+(26年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$845万
+$24,558/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$612万
+$22,010/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="L14" s="22" t="inlineStr">
+        <is>
+          <t>L | 269呎 (1房)
+$563万
+$20,948/呎
+(26年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="M14" s="22" t="inlineStr">
+        <is>
+          <t>M | 386呎 (3房)
+$869万
+$22,514/呎
+(26年-09月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
 $1030万
@@ -18544,7 +18647,7 @@
 (26年-09月-16日)</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
 -
@@ -18552,15 +18655,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
 $852万
 $23,795/呎
-(26年-09月-16日)</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="inlineStr">
+(26年-10月-05日)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
 $787万
@@ -18568,39 +18671,39 @@
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
-$834万
-$23,042/呎
+$843万
+$23,298/呎
+(26年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 387呎 (2房)
+$914万
+$23,605/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="G14" s="22" t="inlineStr">
-        <is>
-          <t>F | 387呎 (2房)
-$935万
-$24,167/呎
-(26年-09月-16日)</t>
-        </is>
-      </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
-$718万
-$22,658/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="I14" s="22" t="inlineStr">
+$789万
+$24,899/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t>H | 264呎 (1房)
 $587万
 $22,227/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="J14" s="20" t="inlineStr">
+(26年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 $845万
@@ -18608,46 +18711,46 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K14" s="22" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
-$612万
-$22,010/呎
-(26年-09月-16日)</t>
-        </is>
-      </c>
-      <c r="L14" s="22" t="inlineStr">
+$619万
+$22,252/呎
+(26年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="L15" s="22" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
 $563万
 $20,948/呎
-(26年-09月-28日)</t>
-        </is>
-      </c>
-      <c r="M14" s="22" t="inlineStr">
+(26年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="M15" s="20" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
-$869万
-$22,514/呎
-(26年-09月-26日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
+$966万
+$25,016/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
-$1030万
-$24,653/呎
-(26年-09月-16日)</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
+$985万
+$23,572/呎
+(26年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
 -
@@ -18655,102 +18758,102 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
-$852万
-$23,795/呎
+$851万
+$23,779/呎
 (26年-09月-16日)</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
-$787万
-$22,036/呎
+$786万
+$22,021/呎
+(26年-10月-05日)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 362呎 (2房)
+$804万
+$22,222/呎
+(26年-10月-05日)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 387呎 (2房)
+$894万
+$23,100/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
-        <is>
-          <t>E | 362呎 (2房)
-$843万
-$23,298/呎
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$702万
+$22,142/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
-        <is>
-          <t>F | 387呎 (2房)
-$914万
-$23,605/呎
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$593万
+$22,456/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$835万
+$24,262/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K16" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$578万
+$20,791/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="H15" s="20" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
-$789万
-$24,899/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I15" s="22" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$587万
-$22,227/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="J15" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
-$845万
-$24,558/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K15" s="22" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$619万
-$22,252/呎
-(26年-09月-16日)</t>
-        </is>
-      </c>
-      <c r="L15" s="22" t="inlineStr">
+      <c r="L16" s="22" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
-$563万
-$20,948/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="M15" s="20" t="inlineStr">
+$557万
+$20,697/呎
+(26年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="M16" s="22" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
-$966万
-$25,016/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="inlineStr">
+$831万
+$21,523/呎
+(26年-09月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
-$985万
-$23,572/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
+$976万
+$23,351/呎
+(26年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
 -
@@ -18758,102 +18861,102 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
-$851万
-$23,779/呎
-(26年-09月-16日)</t>
-        </is>
-      </c>
-      <c r="E16" s="22" t="inlineStr">
+$930万
+$25,978/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
-$786万
-$22,021/呎
+$773万
+$21,650/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
-$804万
-$22,222/呎
+$799万
+$22,085/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
-$894万
-$23,100/呎
+$889万
+$22,960/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
-$702万
-$22,142/呎
+$683万
+$21,552/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr">
+      <c r="I17" s="22" t="inlineStr">
         <is>
           <t>H | 264呎 (1房)
-$593万
-$22,456/呎
-(26年-09月-16日)</t>
-        </is>
-      </c>
-      <c r="J16" s="20" t="inlineStr">
+$591万
+$22,388/呎
+(26年-10月-05日)</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
-$835万
-$24,262/呎
+$832万
+$24,186/呎
 (在售)</t>
         </is>
       </c>
-      <c r="K16" s="22" t="inlineStr">
+      <c r="K17" s="22" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
-$578万
-$20,791/呎
+$576万
+$20,713/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="L16" s="22" t="inlineStr">
+      <c r="L17" s="22" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
-$557万
-$20,697/呎
+$555万
+$20,633/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="M16" s="22" t="inlineStr">
+      <c r="M17" s="22" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
-$831万
-$21,523/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
+$816万
+$21,148/呎
+(26年-09月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
-$976万
-$23,351/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
+$925万
+$22,130/呎
+(26年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
 -
@@ -18861,115 +18964,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
-$930万
-$25,978/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E17" s="22" t="inlineStr">
-        <is>
-          <t>D | 357呎 (2房)
-$773万
-$21,650/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr">
-        <is>
-          <t>E | 362呎 (2房)
-$799万
-$22,085/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="G17" s="22" t="inlineStr">
-        <is>
-          <t>F | 387呎 (2房)
-$889万
-$22,960/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="H17" s="22" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
-$683万
-$21,552/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="I17" s="22" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$591万
-$22,388/呎
-(26年-09月-16日)</t>
-        </is>
-      </c>
-      <c r="J17" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
-$832万
-$24,186/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K17" s="22" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$576万
-$20,713/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="L17" s="22" t="inlineStr">
-        <is>
-          <t>L | 269呎 (1房)
-$555万
-$20,633/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="M17" s="22" t="inlineStr">
-        <is>
-          <t>M | 386呎 (3房)
-$816万
-$21,148/呎
-(26年-09月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>A | 418呎 (3房)
-$925万
-$22,130/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>B | 363呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="20" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
-$914万
-$25,517/呎
-(在售)</t>
+$822万
+$22,965/呎
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -18977,7 +18977,7 @@
           <t>D | 357呎 (2房)
 $759万
 $21,262/呎
-(26年-09月-12日)</t>
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -18985,7 +18985,7 @@
           <t>E | 362呎 (2房)
 $785万
 $21,677/呎
-(26年-09月-12日)</t>
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -19001,7 +19001,7 @@
           <t>G | 317呎 (1房)
 $681万
 $21,486/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -19025,7 +19025,7 @@
           <t>K | 278呎 (1房)
 $594万
 $21,373/呎
-(26年-09月-16日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr">
@@ -19041,7 +19041,7 @@
           <t>M | 386呎 (3房)
 $794万
 $20,569/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
     </row>
@@ -19064,7 +19064,7 @@
           <t>B | 363呎 (2房)
 $795万
 $21,895/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -19080,7 +19080,7 @@
           <t>D | 357呎 (2房)
 $747万
 $20,912/呎
-(26年-09月-12日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -19104,7 +19104,7 @@
           <t>G | 317呎 (1房)
 $687万
 $21,659/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -19128,7 +19128,7 @@
           <t>K | 278呎 (1房)
 $592万
 $21,305/呎
-(26年-09月-16日)</t>
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="L19" s="22" t="inlineStr">
@@ -19144,7 +19144,7 @@
           <t>M | 386呎 (3房)
 $792万
 $20,509/呎
-(26年-09月-12日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -19167,7 +19167,7 @@
           <t>B | 363呎 (2房)
 $787万
 $21,687/呎
-(26年-09月-12日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -19183,7 +19183,7 @@
           <t>D | 357呎 (2房)
 $740万
 $20,718/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -19199,7 +19199,7 @@
           <t>F | 387呎 (2房)
 $848万
 $21,912/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -19207,7 +19207,7 @@
           <t>G | 317呎 (1房)
 $677万
 $21,356/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -19231,7 +19231,7 @@
           <t>K | 278呎 (1房)
 $590万
 $21,241/呎
-(26年-09月-16日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr">
@@ -19270,7 +19270,7 @@
           <t>B | 363呎 (2房)
 $782万
 $21,548/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -19286,7 +19286,7 @@
           <t>D | 357呎 (2房)
 $727万
 $20,362/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -19342,7 +19342,7 @@
           <t>L | 269呎 (1房)
 $548万
 $20,379/呎
-(26年-09月-12日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="M21" s="21" t="inlineStr">
@@ -19365,7 +19365,7 @@
           <t>A | 418呎 (3房)
 $946万
 $22,638/呎
-(26年-09月-16日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -19389,7 +19389,7 @@
           <t>D | 357呎 (2房)
 $722万
 $20,234/呎
-(26年-09月-12日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -19397,7 +19397,7 @@
           <t>E | 362呎 (2房)
 $745万
 $20,591/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -19405,7 +19405,7 @@
           <t>F | 387呎 (2房)
 $838万
 $21,661/呎
-(26年-09月-12日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -19413,7 +19413,7 @@
           <t>G | 317呎 (1房)
 $673万
 $21,228/呎
-(26年-09月-12日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -19437,7 +19437,7 @@
           <t>K | 278呎 (1房)
 $587万
 $21,108/呎
-(26年-09月-16日)</t>
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="L22" s="22" t="inlineStr">
@@ -19500,7 +19500,7 @@
           <t>E | 362呎 (2房)
 $745万
 $20,591/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -19508,10 +19508,113 @@
           <t>F | 387呎 (2房)
 $838万
 $21,661/呎
+(26年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$671万
+$21,163/呎
+(26年-10月-05日)</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$580万
+$21,972/呎
+(26年-10月-05日)</t>
+        </is>
+      </c>
+      <c r="J23" s="20" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$818万
+$23,785/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K23" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$585万
+$21,043/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="L23" s="22" t="inlineStr">
+        <is>
+          <t>L | 269呎 (1房)
+$557万
+$20,701/呎
+(26年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="M23" s="20" t="inlineStr">
+        <is>
+          <t>M | 386呎 (3房)
+$934万
+$24,199/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 418呎 (3房)
+$869万
+$20,790/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 363呎 (2房)
+$767万
+$21,131/呎
+(26年-09月-24日)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 357呎 (2房)
+$713万
+$19,974/呎
+(26年-10月-05日)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 362呎 (2房)
+$736万
+$20,320/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 387呎 (2房)
+$818万
+$21,144/呎
+(26年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
 $671万
@@ -19519,23 +19622,23 @@
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="I23" s="22" t="inlineStr">
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>H | 264呎 (1房)
 $580万
 $21,972/呎
-(26年-09月-16日)</t>
-        </is>
-      </c>
-      <c r="J23" s="20" t="inlineStr">
+(26年-09月-22日)</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 $818万
-$23,785/呎
+$23,773/呎
 (在售)</t>
         </is>
       </c>
-      <c r="K23" s="22" t="inlineStr">
+      <c r="K24" s="22" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
 $585万
@@ -19543,46 +19646,46 @@
 (26年-09月-16日)</t>
         </is>
       </c>
-      <c r="L23" s="22" t="inlineStr">
+      <c r="L24" s="22" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
-$557万
-$20,701/呎
+$545万
+$20,252/呎
 (26年-09月-12日)</t>
         </is>
       </c>
-      <c r="M23" s="20" t="inlineStr">
+      <c r="M24" s="22" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
-$934万
-$24,199/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="inlineStr">
+$782万
+$20,259/呎
+(26年-09月-28日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
-$869万
-$20,790/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="inlineStr">
+$867万
+$20,749/呎
+(26年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
-$767万
-$21,131/呎
-(26年-09月-24日)</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="inlineStr">
+$758万
+$20,888/呎
+(26年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
 -
@@ -19590,115 +19693,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
-        <is>
-          <t>D | 357呎 (2房)
-$713万
-$19,974/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="F24" s="22" t="inlineStr">
-        <is>
-          <t>E | 362呎 (2房)
-$736万
-$20,320/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="G24" s="22" t="inlineStr">
-        <is>
-          <t>F | 387呎 (2房)
-$818万
-$21,144/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="H24" s="22" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
-$671万
-$21,163/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="I24" s="22" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$580万
-$21,972/呎
-(26年-09月-22日)</t>
-        </is>
-      </c>
-      <c r="J24" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
-$818万
-$23,773/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K24" s="22" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$585万
-$21,043/呎
-(26年-09月-16日)</t>
-        </is>
-      </c>
-      <c r="L24" s="22" t="inlineStr">
-        <is>
-          <t>L | 269呎 (1房)
-$545万
-$20,252/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="M24" s="22" t="inlineStr">
-        <is>
-          <t>M | 386呎 (3房)
-$782万
-$20,259/呎
-(26年-09月-28日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B25" s="22" t="inlineStr">
-        <is>
-          <t>A | 418呎 (3房)
-$867万
-$20,749/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="inlineStr">
-        <is>
-          <t>B | 363呎 (2房)
-$758万
-$20,888/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
 $704万
 $19,732/呎
-(26年-09月-12日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -19706,7 +19706,7 @@
           <t>E | 362呎 (2房)
 $723万
 $19,981/呎
-(26年-09月-12日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -19714,7 +19714,7 @@
           <t>F | 387呎 (2房)
 $807万
 $20,865/呎
-(26年-09月-12日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -19722,7 +19722,7 @@
           <t>G | 317呎 (1房)
 $675万
 $21,300/呎
-(26年-09月-12日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">

--- a/files/九龙-红磡-映汇.xlsx
+++ b/files/九龙-红磡-映汇.xlsx
@@ -1774,7 +1774,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6598,7 +6598,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6916,14 +6916,14 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
-        <v>5834900</v>
+        <v>5669100</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>21691</v>
+        <v>21075</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
@@ -6931,10 +6931,10 @@
         </is>
       </c>
       <c r="K99" s="5" t="n">
-        <v>5834900</v>
+        <v>5669100</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>21691</v>
+        <v>21075</v>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10415,23 +10415,23 @@
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
-        <v>9300000</v>
+        <v>8370000</v>
       </c>
       <c r="I155" s="5" t="n">
-        <v>25978</v>
+        <v>23380</v>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K155" s="5" t="n">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="M155" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N155" s="3" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11800,7 +11800,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13641,23 +13641,23 @@
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
-        <v>9369000</v>
+        <v>8432100</v>
       </c>
       <c r="I206" s="5" t="n">
-        <v>24272</v>
+        <v>21845</v>
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K206" s="5" t="n">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N206" s="3" t="inlineStr">
@@ -13708,7 +13708,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -15088,7 +15088,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15398,7 +15398,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15460,7 +15460,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15522,7 +15522,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15584,7 +15584,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15840,7 +15840,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -16150,7 +16150,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -16786,7 +16786,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -17519,7 +17519,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -17529,7 +17529,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -17773,7 +17773,7 @@
           <t>H | 264呎 (1房)
 $625万
 $23,684/呎
-(26年-09月-12日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -17844,7 +17844,7 @@
           <t>D | 357呎 (2房)
 $833万
 $23,324/呎
-(26年-09月-12日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -17979,7 +17979,7 @@
           <t>H | 264呎 (1房)
 $608万
 $23,018/呎
-(26年-09月-12日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -17995,7 +17995,7 @@
           <t>K | 278呎 (1房)
 $607万
 $21,820/呎
-(26年-09月-12日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="L8" s="22" t="inlineStr">
@@ -18026,7 +18026,7 @@
           <t>A | 418呎 (3房)
 $1049万
 $25,101/呎
-(26年-09月-12日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -18114,7 +18114,7 @@
           <t>M | 386呎 (3房)
 $875万
 $22,677/呎
-(26年-09月-12日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
     </row>
@@ -18153,7 +18153,7 @@
           <t>D | 357呎 (2房)
 $812万
 $22,745/呎
-(26年-09月-12日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -18177,7 +18177,7 @@
           <t>G | 317呎 (1房)
 $710万
 $22,392/呎
-(26年-09月-12日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -18209,7 +18209,7 @@
           <t>L | 269呎 (1房)
 $583万
 $21,691/呎
-(26年-09月-12日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="M10" s="22" t="inlineStr">
@@ -18359,7 +18359,7 @@
           <t>D | 357呎 (2房)
 $796万
 $22,293/呎
-(26年-09月-12日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -18407,7 +18407,7 @@
           <t>K | 278呎 (1房)
 $592万
 $21,312/呎
-(26年-09月-12日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="L12" s="22" t="inlineStr">
@@ -18423,7 +18423,7 @@
           <t>M | 386呎 (3房)
 $827万
 $21,427/呎
-(26年-09月-12日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
     </row>
@@ -18462,7 +18462,7 @@
           <t>D | 357呎 (2房)
 $791万
 $22,165/呎
-(26年-09月-12日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -18510,15 +18510,15 @@
           <t>K | 278呎 (1房)
 $589万
 $21,186/呎
-(26年-09月-12日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="L13" s="22" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
-$583万
-$21,691/呎
-(26年-09月-29日)</t>
+$567万
+$21,075/呎
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="M13" s="22" t="inlineStr">
@@ -18557,7 +18557,7 @@
           <t>C | 358呎 (2房)
 $852万
 $23,795/呎
-(26年-09月-16日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -18565,7 +18565,7 @@
           <t>D | 357呎 (2房)
 $787万
 $22,036/呎
-(26年-09月-12日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -18581,7 +18581,7 @@
           <t>F | 387呎 (2房)
 $935万
 $24,167/呎
-(26年-09月-16日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -18644,7 +18644,7 @@
           <t>A | 418呎 (3房)
 $1030万
 $24,653/呎
-(26年-09月-16日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -18668,7 +18668,7 @@
           <t>D | 357呎 (2房)
 $787万
 $22,036/呎
-(26年-09月-12日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -18684,7 +18684,7 @@
           <t>F | 387呎 (2房)
 $914万
 $23,605/呎
-(26年-09月-12日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -18787,7 +18787,7 @@
           <t>F | 387呎 (2房)
 $894万
 $23,100/呎
-(26年-09月-12日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -18795,7 +18795,7 @@
           <t>G | 317呎 (1房)
 $702万
 $22,142/呎
-(26年-09月-12日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -18803,7 +18803,7 @@
           <t>H | 264呎 (1房)
 $593万
 $22,456/呎
-(26年-09月-16日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -18819,7 +18819,7 @@
           <t>K | 278呎 (1房)
 $578万
 $20,791/呎
-(26年-09月-12日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="L16" s="22" t="inlineStr">
@@ -18861,12 +18861,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
-$930万
-$25,978/呎
-(在售)</t>
+$837万
+$23,380/呎
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -18874,7 +18874,7 @@
           <t>D | 357呎 (2房)
 $773万
 $21,650/呎
-(26年-09月-12日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -18882,7 +18882,7 @@
           <t>E | 362呎 (2房)
 $799万
 $22,085/呎
-(26年-09月-12日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -18890,7 +18890,7 @@
           <t>F | 387呎 (2房)
 $889万
 $22,960/呎
-(26年-09月-12日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -18898,7 +18898,7 @@
           <t>G | 317呎 (1房)
 $683万
 $21,552/呎
-(26年-09月-12日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -18922,7 +18922,7 @@
           <t>K | 278呎 (1房)
 $576万
 $20,713/呎
-(26年-09月-12日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="L17" s="22" t="inlineStr">
@@ -18930,7 +18930,7 @@
           <t>L | 269呎 (1房)
 $555万
 $20,633/呎
-(26年-09月-12日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="M17" s="22" t="inlineStr">
@@ -18993,7 +18993,7 @@
           <t>F | 387呎 (2房)
 $872万
 $22,542/呎
-(26年-09月-12日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -19009,7 +19009,7 @@
           <t>H | 264呎 (1房)
 $596万
 $22,567/呎
-(26年-09月-16日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -19033,7 +19033,7 @@
           <t>L | 269呎 (1房)
 $553万
 $20,570/呎
-(26年-09月-12日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="M18" s="22" t="inlineStr">
@@ -19056,7 +19056,7 @@
           <t>A | 418呎 (3房)
 $900万
 $21,527/呎
-(26年-09月-12日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -19088,7 +19088,7 @@
           <t>E | 362呎 (2房)
 $771万
 $21,299/呎
-(26年-09月-12日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -19096,7 +19096,7 @@
           <t>F | 387呎 (2房)
 $857万
 $22,155/呎
-(26年-09月-12日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -19112,7 +19112,7 @@
           <t>H | 264呎 (1房)
 $594万
 $22,495/呎
-(26年-09月-16日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -19136,7 +19136,7 @@
           <t>L | 269呎 (1房)
 $552万
 $20,506/呎
-(26年-09月-12日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="M19" s="22" t="inlineStr">
@@ -19191,7 +19191,7 @@
           <t>E | 362呎 (2房)
 $783万
 $21,638/呎
-(26年-09月-12日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -19239,7 +19239,7 @@
           <t>L | 269呎 (1房)
 $550万
 $20,442/呎
-(26年-09月-12日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="M20" s="21" t="inlineStr">
@@ -19294,7 +19294,7 @@
           <t>E | 362呎 (2房)
 $770万
 $21,264/呎
-(26年-09月-12日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -19310,7 +19310,7 @@
           <t>G | 317呎 (1房)
 $699万
 $22,055/呎
-(26年-09月-20日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -19421,7 +19421,7 @@
           <t>H | 264呎 (1房)
 $588万
 $22,288/呎
-(26年-09月-16日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -19445,15 +19445,15 @@
           <t>L | 269呎 (1房)
 $546万
 $20,315/呎
-(26年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="M22" s="20" t="inlineStr">
+(26年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="M22" s="22" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
-$937万
-$24,272/呎
-(在售)</t>
+$843万
+$21,845/呎
+(26年-10月-06日)</t>
         </is>
       </c>
     </row>
@@ -19468,7 +19468,7 @@
           <t>A | 418呎 (3房)
 $946万
 $22,638/呎
-(26年-09月-16日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -19492,7 +19492,7 @@
           <t>D | 357呎 (2房)
 $722万
 $20,234/呎
-(26年-09月-12日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -19540,7 +19540,7 @@
           <t>K | 278呎 (1房)
 $585万
 $21,043/呎
-(26年-09月-16日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="L23" s="22" t="inlineStr">
@@ -19571,7 +19571,7 @@
           <t>A | 418呎 (3房)
 $869万
 $20,790/呎
-(26年-09月-12日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -19603,7 +19603,7 @@
           <t>E | 362呎 (2房)
 $736万
 $20,320/呎
-(26年-09月-12日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -19611,7 +19611,7 @@
           <t>F | 387呎 (2房)
 $818万
 $21,144/呎
-(26年-09月-12日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -19619,7 +19619,7 @@
           <t>G | 317呎 (1房)
 $671万
 $21,163/呎
-(26年-09月-12日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -19627,7 +19627,7 @@
           <t>H | 264呎 (1房)
 $580万
 $21,972/呎
-(26年-09月-22日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -19643,7 +19643,7 @@
           <t>K | 278呎 (1房)
 $585万
 $21,043/呎
-(26年-09月-16日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr">
@@ -19730,7 +19730,7 @@
           <t>H | 264呎 (1房)
 $585万
 $22,171/呎
-(26年-09月-16日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -19849,7 +19849,7 @@
           <t>K | 240呎 (1房)
 $613万
 $25,550/呎
-(26年-09月-16日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr">

--- a/files/九龙-红磡-映汇.xlsx
+++ b/files/九龙-红磡-映汇.xlsx
@@ -1650,7 +1650,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -2669,23 +2669,23 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
-        <v>11166000</v>
+        <v>10049400</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>28853</v>
+        <v>25967</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="5" t="n">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -5908,14 +5908,14 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
-        <v>8787800</v>
+        <v>8787000</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>24547</v>
+        <v>24545</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="K83" s="5" t="n">
-        <v>8787800</v>
+        <v>8787000</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>24547</v>
+        <v>24545</v>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -11800,14 +11800,14 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
-        <v>7710400</v>
+        <v>7625700</v>
       </c>
       <c r="I177" s="5" t="n">
-        <v>21299</v>
+        <v>21065</v>
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
@@ -11815,10 +11815,10 @@
         </is>
       </c>
       <c r="K177" s="5" t="n">
-        <v>7710400</v>
+        <v>7625700</v>
       </c>
       <c r="L177" s="5" t="n">
-        <v>21299</v>
+        <v>21065</v>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -13010,7 +13010,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -13258,7 +13258,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -16026,7 +16026,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -16724,7 +16724,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -17519,7 +17519,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -17529,7 +17529,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>182</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -17789,7 +17789,7 @@
           <t>K | 278呎 (1房)
 $624万
 $22,449/呎
-(26年-09月-12日)</t>
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="L6" s="22" t="inlineStr">
@@ -17855,12 +17855,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t>F | 387呎 (3房)
-$1117万
-$28,853/呎
-(在售)</t>
+$1005万
+$25,967/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -17939,7 +17939,7 @@
           <t>C | 358呎 (2房)
 $894万
 $24,969/呎
-(26年-09月-16日)</t>
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -18247,8 +18247,8 @@
         <is>
           <t>C | 358呎 (2房)
 $879万
-$24,547/呎
-(26年-09月-16日)</t>
+$24,545/呎
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -18565,7 +18565,7 @@
           <t>D | 357呎 (2房)
 $787万
 $22,036/呎
-(26年-10月-06日)</t>
+(26年-09月-12日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -18613,7 +18613,7 @@
           <t>K | 278呎 (1房)
 $612万
 $22,010/呎
-(26年-09月-16日)</t>
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="L14" s="22" t="inlineStr">
@@ -19086,9 +19086,9 @@
       <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
-$771万
-$21,299/呎
-(26年-10月-07日)</t>
+$763万
+$21,065/呎
+(26年-09月-12日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -19215,7 +19215,7 @@
           <t>H | 264呎 (1房)
 $592万
 $22,426/呎
-(26年-09月-16日)</t>
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -19302,7 +19302,7 @@
           <t>F | 387呎 (2房)
 $863万
 $22,288/呎
-(26年-09月-16日)</t>
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -19318,7 +19318,7 @@
           <t>H | 264呎 (1房)
 $597万
 $22,603/呎
-(26年-09月-16日)</t>
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -19334,7 +19334,7 @@
           <t>K | 278呎 (1房)
 $589万
 $21,176/呎
-(26年-09月-16日)</t>
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="L21" s="22" t="inlineStr">
@@ -19746,7 +19746,7 @@
           <t>K | 278呎 (1房)
 $596万
 $21,448/呎
-(26年-09月-16日)</t>
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr">
@@ -19857,7 +19857,7 @@
           <t>L | 231呎 (1房)
 $605万
 $26,200/呎
-(26年-09月-16日)</t>
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="M26" s="20" t="inlineStr">

--- a/files/九龙-红磡-映汇.xlsx
+++ b/files/九龙-红磡-映汇.xlsx
@@ -9668,7 +9668,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -18763,7 +18763,7 @@
           <t>C | 358呎 (2房)
 $851万
 $23,779/呎
-(26年-09月-16日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">

--- a/files/九龙-红磡-映汇.xlsx
+++ b/files/九龙-红磡-映汇.xlsx
@@ -2868,7 +2868,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -17836,7 +17836,7 @@
           <t>C | 358呎 (2房)
 $901万
 $25,175/呎
-(26年-09月-23日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -18969,7 +18969,7 @@
           <t>C | 358呎 (2房)
 $822万
 $22,965/呎
-(26年-10月-02日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">

--- a/files/九龙-红磡-映汇.xlsx
+++ b/files/九龙-红磡-映汇.xlsx
@@ -1901,23 +1901,23 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>11355000</v>
+        <v>10219500</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>29341</v>
+        <v>26407</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="5" t="n">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -2095,23 +2095,23 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>10179000</v>
+        <v>9161100</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>28433</v>
+        <v>25590</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="5" t="n">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -3830,14 +3830,14 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
-        <v>8753200</v>
+        <v>8657100</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>22677</v>
+        <v>22428</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -3845,10 +3845,10 @@
         </is>
       </c>
       <c r="K50" s="5" t="n">
-        <v>8753200</v>
+        <v>8657100</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>22677</v>
+        <v>22428</v>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7730,14 +7730,14 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
-        <v>6118800</v>
+        <v>6051600</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>22010</v>
+        <v>21768</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
@@ -7745,10 +7745,10 @@
         </is>
       </c>
       <c r="K112" s="5" t="n">
-        <v>6118800</v>
+        <v>6051600</v>
       </c>
       <c r="L112" s="5" t="n">
-        <v>22010</v>
+        <v>21768</v>
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
@@ -7787,23 +7787,23 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
-        <v>8448000</v>
+        <v>7603200</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>24558</v>
+        <v>22102</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K113" s="5" t="n">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N113" s="3" t="inlineStr">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -12614,14 +12614,14 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
-        <v>7396400</v>
+        <v>7315200</v>
       </c>
       <c r="I190" s="5" t="n">
-        <v>20718</v>
+        <v>20491</v>
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
@@ -12629,10 +12629,10 @@
         </is>
       </c>
       <c r="K190" s="5" t="n">
-        <v>7396400</v>
+        <v>7315200</v>
       </c>
       <c r="L190" s="5" t="n">
-        <v>20718</v>
+        <v>20491</v>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -14770,14 +14770,14 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
-        <v>8382900</v>
+        <v>8290800</v>
       </c>
       <c r="I224" s="5" t="n">
-        <v>21661</v>
+        <v>21423</v>
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
@@ -14785,10 +14785,10 @@
         </is>
       </c>
       <c r="K224" s="5" t="n">
-        <v>8382900</v>
+        <v>8290800</v>
       </c>
       <c r="L224" s="5" t="n">
-        <v>21661</v>
+        <v>21423</v>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
@@ -15902,14 +15902,14 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
-        <v>7882400</v>
+        <v>7795800</v>
       </c>
       <c r="I242" s="5" t="n">
-        <v>20421</v>
+        <v>20196</v>
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
@@ -15917,10 +15917,10 @@
         </is>
       </c>
       <c r="K242" s="5" t="n">
-        <v>7882400</v>
+        <v>7795800</v>
       </c>
       <c r="L242" s="5" t="n">
-        <v>20421</v>
+        <v>20196</v>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
@@ -16150,14 +16150,14 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
-        <v>5853100</v>
+        <v>5788800</v>
       </c>
       <c r="I246" s="5" t="n">
-        <v>22171</v>
+        <v>21927</v>
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
@@ -16165,10 +16165,10 @@
         </is>
       </c>
       <c r="K246" s="5" t="n">
-        <v>5853100</v>
+        <v>5788800</v>
       </c>
       <c r="L246" s="5" t="n">
-        <v>22171</v>
+        <v>21927</v>
       </c>
       <c r="M246" s="3" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -17529,7 +17529,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>185</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -17728,12 +17728,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
-$1018万
-$28,433/呎
-(在售)</t>
+$916万
+$25,590/呎
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -17752,12 +17752,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t>F | 387呎 (3房)
-$1136万
-$29,341/呎
-(在售)</t>
+$1022万
+$26,407/呎
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -18042,7 +18042,7 @@
           <t>C | 358呎 (2房)
 $886万
 $24,760/呎
-(26年-09月-27日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -18112,9 +18112,9 @@
       <c r="M9" s="22" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
-$875万
-$22,677/呎
-(26年-10月-08日)</t>
+$866万
+$22,428/呎
+(26年-09月-12日)</t>
         </is>
       </c>
     </row>
@@ -18600,7 +18600,110 @@
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="J14" s="20" t="inlineStr">
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$760万
+$22,102/呎
+(26年-10月-21日)</t>
+        </is>
+      </c>
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$605万
+$21,768/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="L14" s="22" t="inlineStr">
+        <is>
+          <t>L | 269呎 (1房)
+$563万
+$20,948/呎
+(26年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="M14" s="22" t="inlineStr">
+        <is>
+          <t>M | 386呎 (3房)
+$869万
+$22,514/呎
+(26年-10月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 418呎 (3房)
+$1030万
+$24,653/呎
+(26年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 363呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 358呎 (2房)
+$852万
+$23,795/呎
+(26年-10月-05日)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 357呎 (2房)
+$787万
+$22,036/呎
+(26年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 362呎 (2房)
+$843万
+$23,298/呎
+(26年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 387呎 (2房)
+$914万
+$23,605/呎
+(26年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$789万
+$24,899/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$587万
+$22,227/呎
+(26年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>J | 344呎 (2房)
 $845万
@@ -18608,46 +18711,46 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K14" s="22" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t>K | 278呎 (1房)
-$612万
-$22,010/呎
-(26年-10月-09日)</t>
-        </is>
-      </c>
-      <c r="L14" s="22" t="inlineStr">
+$619万
+$22,252/呎
+(26年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="L15" s="22" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
 $563万
 $20,948/呎
-(26年-09月-28日)</t>
-        </is>
-      </c>
-      <c r="M14" s="22" t="inlineStr">
+(26年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="M15" s="20" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
-$869万
-$22,514/呎
-(26年-09月-26日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
+$966万
+$25,016/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 418呎 (3房)
-$1030万
-$24,653/呎
-(26年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
+$985万
+$23,572/呎
+(26年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
 -
@@ -18655,102 +18758,102 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
-$852万
-$23,795/呎
+$851万
+$23,779/呎
+(26年-10月-15日)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 357呎 (2房)
+$786万
+$22,021/呎
 (26年-10月-05日)</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>D | 357呎 (2房)
-$787万
-$22,036/呎
-(26年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>E | 362呎 (2房)
-$843万
-$23,298/呎
-(26年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="G15" s="22" t="inlineStr">
+$804万
+$22,222/呎
+(26年-10月-05日)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
-$914万
-$23,605/呎
-(26年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="H15" s="20" t="inlineStr">
+$894万
+$23,100/呎
+(26年-10月-07日)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
-$789万
-$24,899/呎
+$702万
+$22,142/呎
+(26年-10月-07日)</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$593万
+$22,456/呎
+(26年-10月-08日)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$835万
+$24,262/呎
 (在售)</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$587万
-$22,227/呎
+      <c r="K16" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$578万
+$20,791/呎
+(26年-10月-07日)</t>
+        </is>
+      </c>
+      <c r="L16" s="22" t="inlineStr">
+        <is>
+          <t>L | 269呎 (1房)
+$557万
+$20,697/呎
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="J15" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
-$845万
-$24,558/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K15" s="22" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$619万
-$22,252/呎
+      <c r="M16" s="22" t="inlineStr">
+        <is>
+          <t>M | 386呎 (3房)
+$831万
+$21,523/呎
+(26年-09月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 418呎 (3房)
+$976万
+$23,351/呎
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="L15" s="22" t="inlineStr">
-        <is>
-          <t>L | 269呎 (1房)
-$563万
-$20,948/呎
-(26年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="M15" s="20" t="inlineStr">
-        <is>
-          <t>M | 386呎 (3房)
-$966万
-$25,016/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="inlineStr">
-        <is>
-          <t>A | 418呎 (3房)
-$985万
-$23,572/呎
-(26年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
 -
@@ -18758,102 +18861,102 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
-$851万
-$23,779/呎
-(26年-10月-15日)</t>
-        </is>
-      </c>
-      <c r="E16" s="22" t="inlineStr">
+$837万
+$23,380/呎
+(26年-10月-22日)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
-$786万
-$22,021/呎
+$773万
+$21,650/呎
+(26年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 362呎 (2房)
+$799万
+$22,085/呎
+(26年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 387呎 (2房)
+$889万
+$22,960/呎
+(26年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>G | 317呎 (1房)
+$683万
+$21,552/呎
+(26年-10月-08日)</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
+        <is>
+          <t>H | 264呎 (1房)
+$591万
+$22,388/呎
 (26年-10月-05日)</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
-        <is>
-          <t>E | 362呎 (2房)
-$804万
-$22,222/呎
-(26年-10月-05日)</t>
-        </is>
-      </c>
-      <c r="G16" s="22" t="inlineStr">
-        <is>
-          <t>F | 387呎 (2房)
-$894万
-$23,100/呎
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>J | 344呎 (2房)
+$832万
+$24,186/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K17" s="22" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$576万
+$20,713/呎
 (26年-10月-07日)</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
-$702万
-$22,142/呎
-(26年-10月-07日)</t>
-        </is>
-      </c>
-      <c r="I16" s="22" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$593万
-$22,456/呎
-(26年-10月-08日)</t>
-        </is>
-      </c>
-      <c r="J16" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
-$835万
-$24,262/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K16" s="22" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$578万
-$20,791/呎
-(26年-10月-07日)</t>
-        </is>
-      </c>
-      <c r="L16" s="22" t="inlineStr">
+      <c r="L17" s="22" t="inlineStr">
         <is>
           <t>L | 269呎 (1房)
-$557万
-$20,697/呎
+$555万
+$20,633/呎
+(26年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="M17" s="22" t="inlineStr">
+        <is>
+          <t>M | 386呎 (3房)
+$816万
+$21,148/呎
+(26年-09月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 418呎 (3房)
+$925万
+$22,130/呎
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="M16" s="22" t="inlineStr">
-        <is>
-          <t>M | 386呎 (3房)
-$831万
-$21,523/呎
-(26年-09月-29日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>A | 418呎 (3房)
-$976万
-$23,351/呎
-(26年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 363呎 (2房)
 -
@@ -18861,109 +18964,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
-        <is>
-          <t>C | 358呎 (2房)
-$837万
-$23,380/呎
-(26年-10月-05日)</t>
-        </is>
-      </c>
-      <c r="E17" s="22" t="inlineStr">
-        <is>
-          <t>D | 357呎 (2房)
-$773万
-$21,650/呎
-(26年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr">
-        <is>
-          <t>E | 362呎 (2房)
-$799万
-$22,085/呎
-(26年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="G17" s="22" t="inlineStr">
-        <is>
-          <t>F | 387呎 (2房)
-$889万
-$22,960/呎
-(26年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="H17" s="22" t="inlineStr">
-        <is>
-          <t>G | 317呎 (1房)
-$683万
-$21,552/呎
-(26年-10月-08日)</t>
-        </is>
-      </c>
-      <c r="I17" s="22" t="inlineStr">
-        <is>
-          <t>H | 264呎 (1房)
-$591万
-$22,388/呎
-(26年-10月-05日)</t>
-        </is>
-      </c>
-      <c r="J17" s="20" t="inlineStr">
-        <is>
-          <t>J | 344呎 (2房)
-$832万
-$24,186/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K17" s="22" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$576万
-$20,713/呎
-(26年-10月-07日)</t>
-        </is>
-      </c>
-      <c r="L17" s="22" t="inlineStr">
-        <is>
-          <t>L | 269呎 (1房)
-$555万
-$20,633/呎
-(26年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="M17" s="22" t="inlineStr">
-        <is>
-          <t>M | 386呎 (3房)
-$816万
-$21,148/呎
-(26年-09月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>A | 418呎 (3房)
-$925万
-$22,130/呎
-(26年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>B | 363呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 358呎 (2房)
@@ -19072,7 +19072,7 @@
           <t>C | 358呎 (2房)
 $800万
 $22,344/呎
-(26年-09月-17日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -19181,9 +19181,9 @@
       <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 357呎 (2房)
-$740万
-$20,718/呎
-(26年-09月-30日)</t>
+$732万
+$20,491/呎
+(26年-09月-12日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -19453,7 +19453,7 @@
           <t>M | 386呎 (3房)
 $843万
 $21,845/呎
-(26年-10月-06日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -19506,9 +19506,9 @@
       <c r="G23" s="22" t="inlineStr">
         <is>
           <t>F | 387呎 (2房)
-$838万
-$21,661/呎
-(26年-09月-30日)</t>
+$829万
+$21,423/呎
+(26年-09月-12日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -19728,9 +19728,9 @@
       <c r="I25" s="22" t="inlineStr">
         <is>
           <t>H | 264呎 (1房)
-$585万
-$22,171/呎
-(26年-10月-07日)</t>
+$579万
+$21,927/呎
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -19760,9 +19760,9 @@
       <c r="M25" s="22" t="inlineStr">
         <is>
           <t>M | 386呎 (3房)
-$788万
-$20,421/呎
-(26年-09月-28日)</t>
+$780万
+$20,196/呎
+(26年-09月-12日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-红磡-映汇.xlsx
+++ b/files/九龙-红磡-映汇.xlsx
@@ -1774,14 +1774,14 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>6252600</v>
+        <v>6183900</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>23684</v>
+        <v>23424</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>6252600</v>
+        <v>6183900</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>23684</v>
+        <v>23424</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -5908,14 +5908,14 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
-        <v>8787000</v>
+        <v>8787800</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>24545</v>
+        <v>24547</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="K83" s="5" t="n">
-        <v>8787000</v>
+        <v>8787800</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>24545</v>
+        <v>24547</v>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
@@ -7916,14 +7916,14 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
-        <v>7182600</v>
+        <v>7103700</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>22658</v>
+        <v>22409</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
@@ -7931,10 +7931,10 @@
         </is>
       </c>
       <c r="K115" s="5" t="n">
-        <v>7182600</v>
+        <v>7103700</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>22658</v>
+        <v>22409</v>
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
@@ -17771,9 +17771,9 @@
       <c r="I6" s="22" t="inlineStr">
         <is>
           <t>H | 264呎 (1房)
-$625万
-$23,684/呎
-(26年-10月-06日)</t>
+$618万
+$23,424/呎
+(26年-09月-12日)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -17860,7 +17860,7 @@
           <t>F | 387呎 (3房)
 $1005万
 $25,967/呎
-(26年-10月-12日)</t>
+(26年-10月-29日)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -18247,8 +18247,8 @@
         <is>
           <t>C | 358呎 (2房)
 $879万
-$24,545/呎
-(26年-10月-13日)</t>
+$24,547/呎
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -18587,9 +18587,9 @@
       <c r="H14" s="22" t="inlineStr">
         <is>
           <t>G | 317呎 (1房)
-$718万
-$22,658/呎
-(26年-09月-30日)</t>
+$710万
+$22,409/呎
+(26年-09月-12日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
